--- a/Data/FlightPlan/FPL_24OCT26.xlsx
+++ b/Data/FlightPlan/FPL_24OCT26.xlsx
@@ -218,6 +218,9 @@
     <t>07:35</t>
   </si>
   <si>
+    <t>08:12</t>
+  </si>
+  <si>
     <t>TPE</t>
   </si>
   <si>
@@ -1211,27 +1214,27 @@
     <t>05:55</t>
   </si>
   <si>
+    <t>813A *</t>
+  </si>
+  <si>
     <t>VN-A677</t>
   </si>
   <si>
+    <t>DVO</t>
+  </si>
+  <si>
+    <t>23:45</t>
+  </si>
+  <si>
+    <t>VN-A683</t>
+  </si>
+  <si>
     <t>19:40</t>
   </si>
   <si>
     <t>06:15</t>
   </si>
   <si>
-    <t>813A *</t>
-  </si>
-  <si>
-    <t>VN-A683</t>
-  </si>
-  <si>
-    <t>DVO</t>
-  </si>
-  <si>
-    <t>23:45</t>
-  </si>
-  <si>
     <t>VN-A684</t>
   </si>
   <si>
@@ -1340,7 +1343,7 @@
     <t>Total Record(s): 353</t>
   </si>
   <si>
-    <t xml:space="preserve">Generated on  Oct 24, 2026 01:43</t>
+    <t xml:space="preserve">Generated on  Oct 24, 2026 03:07</t>
   </si>
   <si>
     <t>Page 1 of 1</t>
@@ -2497,7 +2500,9 @@
       </c>
       <c r="K25" s="7"/>
       <c r="L25" s="7"/>
-      <c r="M25" s="7"/>
+      <c t="s" r="M25" s="7">
+        <v>69</v>
+      </c>
     </row>
     <row r="26" ht="14.25" customHeight="1">
       <c t="s" r="A26" s="6">
@@ -2520,10 +2525,10 @@
         <v>66</v>
       </c>
       <c t="s" r="H26" s="8">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c t="s" r="I26" s="7">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c t="s" r="J26" s="7">
         <v>40</v>
@@ -2550,16 +2555,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G27" s="8">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c t="s" r="H27" s="8">
         <v>66</v>
       </c>
       <c t="s" r="I27" s="7">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c t="s" r="J27" s="7">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="K27" s="7"/>
       <c r="L27" s="7"/>
@@ -2589,10 +2594,10 @@
         <v>65</v>
       </c>
       <c t="s" r="I28" s="7">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c t="s" r="J28" s="7">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="K28" s="7"/>
       <c r="L28" s="7"/>
@@ -2625,7 +2630,7 @@
       </c>
       <c r="D30" s="7"/>
       <c t="s" r="E30" s="7">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F30" s="7">
         <v>321</v>
@@ -2637,10 +2642,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I30" s="7">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c t="s" r="J30" s="7">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="K30" s="7"/>
       <c r="L30" s="7"/>
@@ -2658,7 +2663,7 @@
       </c>
       <c r="D31" s="7"/>
       <c t="s" r="E31" s="7">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F31" s="7">
         <v>321</v>
@@ -2667,13 +2672,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H31" s="8">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c t="s" r="I31" s="7">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c t="s" r="J31" s="7">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="K31" s="7"/>
       <c r="L31" s="7"/>
@@ -2691,22 +2696,22 @@
       </c>
       <c r="D32" s="7"/>
       <c t="s" r="E32" s="7">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F32" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G32" s="8">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c t="s" r="H32" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I32" s="7">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c t="s" r="J32" s="7">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K32" s="7"/>
       <c r="L32" s="7"/>
@@ -2724,7 +2729,7 @@
       </c>
       <c r="D33" s="7"/>
       <c t="s" r="E33" s="7">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F33" s="7">
         <v>321</v>
@@ -2736,17 +2741,17 @@
         <v>47</v>
       </c>
       <c t="s" r="I33" s="7">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c t="s" r="J33" s="7">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c t="s" r="K33" s="7">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="L33" s="7"/>
       <c t="s" r="M33" s="7">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="34" ht="14.25" customHeight="1">
@@ -2761,7 +2766,7 @@
       </c>
       <c r="D34" s="7"/>
       <c t="s" r="E34" s="7">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F34" s="7">
         <v>321</v>
@@ -2773,10 +2778,10 @@
         <v>38</v>
       </c>
       <c t="s" r="I34" s="7">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c t="s" r="J34" s="7">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K34" s="7"/>
       <c r="L34" s="7"/>
@@ -2809,7 +2814,7 @@
       </c>
       <c r="D36" s="7"/>
       <c t="s" r="E36" s="7">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F36" s="7">
         <v>321</v>
@@ -2821,10 +2826,10 @@
         <v>47</v>
       </c>
       <c t="s" r="I36" s="7">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c t="s" r="J36" s="7">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K36" s="7"/>
       <c r="L36" s="7"/>
@@ -2842,7 +2847,7 @@
       </c>
       <c r="D37" s="7"/>
       <c t="s" r="E37" s="7">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F37" s="7">
         <v>321</v>
@@ -2851,10 +2856,10 @@
         <v>47</v>
       </c>
       <c t="s" r="H37" s="8">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c t="s" r="I37" s="7">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c t="s" r="J37" s="7">
         <v>45</v>
@@ -2875,22 +2880,22 @@
       </c>
       <c r="D38" s="7"/>
       <c t="s" r="E38" s="7">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F38" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G38" s="8">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c t="s" r="H38" s="8">
         <v>47</v>
       </c>
       <c t="s" r="I38" s="7">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c t="s" r="J38" s="7">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="K38" s="7"/>
       <c r="L38" s="7"/>
@@ -2908,7 +2913,7 @@
       </c>
       <c r="D39" s="7"/>
       <c t="s" r="E39" s="7">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F39" s="7">
         <v>321</v>
@@ -2917,10 +2922,10 @@
         <v>47</v>
       </c>
       <c t="s" r="H39" s="8">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c t="s" r="I39" s="7">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c t="s" r="J39" s="7">
         <v>63</v>
@@ -2956,7 +2961,7 @@
       </c>
       <c r="D41" s="7"/>
       <c t="s" r="E41" s="7">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F41" s="7">
         <v>321</v>
@@ -2968,10 +2973,10 @@
         <v>57</v>
       </c>
       <c t="s" r="I41" s="7">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c t="s" r="J41" s="7">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K41" s="7"/>
       <c r="L41" s="7"/>
@@ -2989,7 +2994,7 @@
       </c>
       <c r="D42" s="7"/>
       <c t="s" r="E42" s="7">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F42" s="7">
         <v>321</v>
@@ -3001,10 +3006,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I42" s="7">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c t="s" r="J42" s="7">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="K42" s="7"/>
       <c r="L42" s="7"/>
@@ -3022,7 +3027,7 @@
       </c>
       <c r="D43" s="7"/>
       <c t="s" r="E43" s="7">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F43" s="7">
         <v>321</v>
@@ -3031,13 +3036,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H43" s="8">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c t="s" r="I43" s="7">
         <v>27</v>
       </c>
       <c t="s" r="J43" s="7">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="K43" s="7"/>
       <c r="L43" s="7"/>
@@ -3055,22 +3060,22 @@
       </c>
       <c r="D44" s="7"/>
       <c t="s" r="E44" s="7">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F44" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G44" s="8">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c t="s" r="H44" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I44" s="7">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c t="s" r="J44" s="7">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="K44" s="7"/>
       <c r="L44" s="7"/>
@@ -3103,7 +3108,7 @@
       </c>
       <c r="D46" s="7"/>
       <c t="s" r="E46" s="7">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F46" s="7">
         <v>321</v>
@@ -3115,7 +3120,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I46" s="7">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c t="s" r="J46" s="7">
         <v>36</v>
@@ -3136,7 +3141,7 @@
       </c>
       <c r="D47" s="7"/>
       <c t="s" r="E47" s="7">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F47" s="7">
         <v>321</v>
@@ -3145,13 +3150,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H47" s="8">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c t="s" r="I47" s="7">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c t="s" r="J47" s="7">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="K47" s="7"/>
       <c r="L47" s="7"/>
@@ -3169,19 +3174,19 @@
       </c>
       <c r="D48" s="7"/>
       <c t="s" r="E48" s="7">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F48" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G48" s="8">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c t="s" r="H48" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I48" s="7">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c t="s" r="J48" s="7">
         <v>20</v>
@@ -3202,7 +3207,7 @@
       </c>
       <c r="D49" s="7"/>
       <c t="s" r="E49" s="7">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F49" s="7">
         <v>321</v>
@@ -3211,10 +3216,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H49" s="8">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c t="s" r="I49" s="7">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c t="s" r="J49" s="7">
         <v>48</v>
@@ -3235,13 +3240,13 @@
       </c>
       <c r="D50" s="7"/>
       <c t="s" r="E50" s="7">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F50" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G50" s="8">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c t="s" r="H50" s="8">
         <v>16</v>
@@ -3250,7 +3255,7 @@
         <v>44</v>
       </c>
       <c t="s" r="J50" s="7">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="K50" s="7"/>
       <c r="L50" s="7"/>
@@ -3261,14 +3266,14 @@
         <v>13</v>
       </c>
       <c t="s" r="B51" s="7">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c t="s" r="C51" s="7">
         <v>14</v>
       </c>
       <c r="D51" s="7"/>
       <c t="s" r="E51" s="7">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F51" s="7">
         <v>321</v>
@@ -3277,20 +3282,20 @@
         <v>16</v>
       </c>
       <c t="s" r="H51" s="8">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c t="s" r="I51" s="7">
         <v>25</v>
       </c>
       <c t="s" r="J51" s="7">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c t="s" r="K51" s="7">
         <v>25</v>
       </c>
       <c r="L51" s="7"/>
       <c t="s" r="M51" s="7">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="52" ht="14.25" customHeight="1">
@@ -3298,20 +3303,20 @@
         <v>13</v>
       </c>
       <c t="s" r="B52" s="7">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c t="s" r="C52" s="7">
         <v>14</v>
       </c>
       <c r="D52" s="7"/>
       <c t="s" r="E52" s="7">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F52" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G52" s="8">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c t="s" r="H52" s="8">
         <v>16</v>
@@ -3335,14 +3340,14 @@
         <v>13</v>
       </c>
       <c t="s" r="B53" s="7">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c t="s" r="C53" s="7">
         <v>14</v>
       </c>
       <c r="D53" s="7"/>
       <c t="s" r="E53" s="7">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F53" s="7">
         <v>321</v>
@@ -3354,17 +3359,17 @@
         <v>47</v>
       </c>
       <c t="s" r="I53" s="7">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c t="s" r="J53" s="7">
+        <v>119</v>
+      </c>
+      <c t="s" r="K53" s="7">
         <v>118</v>
-      </c>
-      <c t="s" r="K53" s="7">
-        <v>117</v>
       </c>
       <c r="L53" s="7"/>
       <c t="s" r="M53" s="7">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="54" ht="14.25" customHeight="1">
@@ -3394,7 +3399,7 @@
       </c>
       <c r="D55" s="7"/>
       <c t="s" r="E55" s="7">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F55" s="7">
         <v>321</v>
@@ -3403,13 +3408,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H55" s="8">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c t="s" r="I55" s="7">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c t="s" r="J55" s="7">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="K55" s="7"/>
       <c r="L55" s="7"/>
@@ -3427,22 +3432,22 @@
       </c>
       <c r="D56" s="7"/>
       <c t="s" r="E56" s="7">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F56" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G56" s="8">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c t="s" r="H56" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I56" s="7">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c t="s" r="J56" s="7">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="K56" s="7"/>
       <c r="L56" s="7"/>
@@ -3460,7 +3465,7 @@
       </c>
       <c r="D57" s="7"/>
       <c t="s" r="E57" s="7">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F57" s="7">
         <v>321</v>
@@ -3469,20 +3474,20 @@
         <v>16</v>
       </c>
       <c t="s" r="H57" s="8">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c t="s" r="I57" s="7">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c t="s" r="J57" s="7">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c t="s" r="K57" s="7">
         <v>40</v>
       </c>
       <c r="L57" s="7"/>
       <c t="s" r="M57" s="7">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="58" ht="14.25" customHeight="1">
@@ -3497,13 +3502,13 @@
       </c>
       <c r="D58" s="7"/>
       <c t="s" r="E58" s="7">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F58" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G58" s="8">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c t="s" r="H58" s="8">
         <v>16</v>
@@ -3512,14 +3517,14 @@
         <v>19</v>
       </c>
       <c t="s" r="J58" s="7">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c t="s" r="K58" s="7">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="L58" s="7"/>
       <c t="s" r="M58" s="7">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="59" ht="14.25" customHeight="1">
@@ -3549,7 +3554,7 @@
       </c>
       <c r="D60" s="7"/>
       <c t="s" r="E60" s="7">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F60" s="7">
         <v>321</v>
@@ -3558,10 +3563,10 @@
         <v>47</v>
       </c>
       <c t="s" r="H60" s="8">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c t="s" r="I60" s="7">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c t="s" r="J60" s="7">
         <v>68</v>
@@ -3582,22 +3587,22 @@
       </c>
       <c r="D61" s="7"/>
       <c t="s" r="E61" s="7">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F61" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G61" s="8">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c t="s" r="H61" s="8">
         <v>47</v>
       </c>
       <c t="s" r="I61" s="7">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c t="s" r="J61" s="7">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="K61" s="7"/>
       <c r="L61" s="7"/>
@@ -3615,7 +3620,7 @@
       </c>
       <c r="D62" s="7"/>
       <c t="s" r="E62" s="7">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F62" s="7">
         <v>321</v>
@@ -3624,13 +3629,13 @@
         <v>47</v>
       </c>
       <c t="s" r="H62" s="8">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c t="s" r="I62" s="7">
         <v>58</v>
       </c>
       <c t="s" r="J62" s="7">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="K62" s="7"/>
       <c r="L62" s="7"/>
@@ -3648,22 +3653,22 @@
       </c>
       <c r="D63" s="7"/>
       <c t="s" r="E63" s="7">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F63" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G63" s="8">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c t="s" r="H63" s="8">
         <v>47</v>
       </c>
       <c t="s" r="I63" s="7">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c t="s" r="J63" s="7">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="K63" s="7"/>
       <c r="L63" s="7"/>
@@ -3681,7 +3686,7 @@
       </c>
       <c r="D64" s="7"/>
       <c t="s" r="E64" s="7">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F64" s="7">
         <v>321</v>
@@ -3690,13 +3695,13 @@
         <v>47</v>
       </c>
       <c t="s" r="H64" s="8">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c t="s" r="I64" s="7">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c t="s" r="J64" s="7">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="K64" s="7"/>
       <c r="L64" s="7"/>
@@ -3714,22 +3719,22 @@
       </c>
       <c r="D65" s="7"/>
       <c t="s" r="E65" s="7">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F65" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G65" s="8">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c t="s" r="H65" s="8">
         <v>47</v>
       </c>
       <c t="s" r="I65" s="7">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c t="s" r="J65" s="7">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="K65" s="7"/>
       <c r="L65" s="7"/>
@@ -3747,7 +3752,7 @@
       </c>
       <c r="D66" s="7"/>
       <c t="s" r="E66" s="7">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F66" s="7">
         <v>321</v>
@@ -3756,13 +3761,13 @@
         <v>47</v>
       </c>
       <c t="s" r="H66" s="8">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c t="s" r="I66" s="7">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c t="s" r="J66" s="7">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="K66" s="7"/>
       <c r="L66" s="7"/>
@@ -3780,13 +3785,13 @@
       </c>
       <c r="D67" s="7"/>
       <c t="s" r="E67" s="7">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F67" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G67" s="8">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c t="s" r="H67" s="8">
         <v>47</v>
@@ -3795,7 +3800,7 @@
         <v>28</v>
       </c>
       <c t="s" r="J67" s="7">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="K67" s="7"/>
       <c r="L67" s="7"/>
@@ -3828,7 +3833,7 @@
       </c>
       <c r="D69" s="7"/>
       <c t="s" r="E69" s="7">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F69" s="7">
         <v>321</v>
@@ -3840,10 +3845,10 @@
         <v>23</v>
       </c>
       <c t="s" r="I69" s="7">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c t="s" r="J69" s="7">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="K69" s="7"/>
       <c r="L69" s="7"/>
@@ -3861,7 +3866,7 @@
       </c>
       <c r="D70" s="7"/>
       <c t="s" r="E70" s="7">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F70" s="7">
         <v>321</v>
@@ -3873,10 +3878,10 @@
         <v>47</v>
       </c>
       <c t="s" r="I70" s="7">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c t="s" r="J70" s="7">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="K70" s="7"/>
       <c r="L70" s="7"/>
@@ -3894,7 +3899,7 @@
       </c>
       <c r="D71" s="7"/>
       <c t="s" r="E71" s="7">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F71" s="7">
         <v>321</v>
@@ -3906,10 +3911,10 @@
         <v>66</v>
       </c>
       <c t="s" r="I71" s="7">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c t="s" r="J71" s="7">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="K71" s="7"/>
       <c r="L71" s="7"/>
@@ -3927,7 +3932,7 @@
       </c>
       <c r="D72" s="7"/>
       <c t="s" r="E72" s="7">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F72" s="7">
         <v>321</v>
@@ -3939,10 +3944,10 @@
         <v>47</v>
       </c>
       <c t="s" r="I72" s="7">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c t="s" r="J72" s="7">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="K72" s="7"/>
       <c r="L72" s="7"/>
@@ -3960,7 +3965,7 @@
       </c>
       <c r="D73" s="7"/>
       <c t="s" r="E73" s="7">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F73" s="7">
         <v>321</v>
@@ -3972,10 +3977,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I73" s="7">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c t="s" r="J73" s="7">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="K73" s="7"/>
       <c r="L73" s="7"/>
@@ -3993,7 +3998,7 @@
       </c>
       <c r="D74" s="7"/>
       <c t="s" r="E74" s="7">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F74" s="7">
         <v>321</v>
@@ -4002,13 +4007,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H74" s="8">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c t="s" r="I74" s="7">
         <v>50</v>
       </c>
       <c t="s" r="J74" s="7">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="K74" s="7"/>
       <c r="L74" s="7"/>
@@ -4026,13 +4031,13 @@
       </c>
       <c r="D75" s="7"/>
       <c t="s" r="E75" s="7">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F75" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G75" s="8">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c t="s" r="H75" s="8">
         <v>16</v>
@@ -4041,7 +4046,7 @@
         <v>35</v>
       </c>
       <c t="s" r="J75" s="7">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="K75" s="7"/>
       <c r="L75" s="7"/>
@@ -4074,7 +4079,7 @@
       </c>
       <c r="D77" s="7"/>
       <c t="s" r="E77" s="7">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F77" s="7">
         <v>321</v>
@@ -4086,17 +4091,17 @@
         <v>47</v>
       </c>
       <c t="s" r="I77" s="7">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c t="s" r="J77" s="7">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c t="s" r="K77" s="7">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="L77" s="7"/>
       <c t="s" r="M77" s="7">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="78" ht="14.25" customHeight="1">
@@ -4111,7 +4116,7 @@
       </c>
       <c r="D78" s="7"/>
       <c t="s" r="E78" s="7">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F78" s="7">
         <v>321</v>
@@ -4123,13 +4128,13 @@
         <v>16</v>
       </c>
       <c t="s" r="I78" s="7">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c t="s" r="J78" s="7">
         <v>25</v>
       </c>
       <c t="s" r="K78" s="7">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="L78" s="7"/>
       <c t="s" r="M78" s="7">
@@ -4141,14 +4146,14 @@
         <v>13</v>
       </c>
       <c t="s" r="B79" s="7">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c t="s" r="C79" s="7">
         <v>14</v>
       </c>
       <c r="D79" s="7"/>
       <c t="s" r="E79" s="7">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F79" s="7">
         <v>321</v>
@@ -4160,17 +4165,17 @@
         <v>47</v>
       </c>
       <c t="s" r="I79" s="7">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c t="s" r="J79" s="7">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c t="s" r="K79" s="7">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="L79" s="7"/>
       <c t="s" r="M79" s="7">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="80" ht="15" customHeight="1">
@@ -4200,7 +4205,7 @@
       </c>
       <c r="D81" s="7"/>
       <c t="s" r="E81" s="7">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F81" s="7">
         <v>321</v>
@@ -4212,10 +4217,10 @@
         <v>47</v>
       </c>
       <c t="s" r="I81" s="7">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c t="s" r="J81" s="7">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="K81" s="7"/>
       <c r="L81" s="7"/>
@@ -4233,7 +4238,7 @@
       </c>
       <c r="D82" s="7"/>
       <c t="s" r="E82" s="7">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F82" s="7">
         <v>321</v>
@@ -4245,7 +4250,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I82" s="7">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c t="s" r="J82" s="7">
         <v>21</v>
@@ -4266,7 +4271,7 @@
       </c>
       <c r="D83" s="7"/>
       <c t="s" r="E83" s="7">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F83" s="7">
         <v>321</v>
@@ -4275,13 +4280,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H83" s="8">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c t="s" r="I83" s="7">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c t="s" r="J83" s="7">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="K83" s="7"/>
       <c r="L83" s="7"/>
@@ -4299,19 +4304,19 @@
       </c>
       <c r="D84" s="7"/>
       <c t="s" r="E84" s="7">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F84" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G84" s="8">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c t="s" r="H84" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I84" s="7">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c t="s" r="J84" s="7">
         <v>31</v>
@@ -4347,7 +4352,7 @@
       </c>
       <c r="D86" s="7"/>
       <c t="s" r="E86" s="7">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F86" s="7">
         <v>321</v>
@@ -4359,10 +4364,10 @@
         <v>47</v>
       </c>
       <c t="s" r="I86" s="7">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c t="s" r="J86" s="7">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="K86" s="7"/>
       <c r="L86" s="7"/>
@@ -4380,7 +4385,7 @@
       </c>
       <c r="D87" s="7"/>
       <c t="s" r="E87" s="7">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F87" s="7">
         <v>321</v>
@@ -4389,13 +4394,13 @@
         <v>47</v>
       </c>
       <c t="s" r="H87" s="8">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c t="s" r="I87" s="7">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c t="s" r="J87" s="7">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="K87" s="7"/>
       <c r="L87" s="7"/>
@@ -4413,22 +4418,22 @@
       </c>
       <c r="D88" s="7"/>
       <c t="s" r="E88" s="7">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F88" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G88" s="8">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c t="s" r="H88" s="8">
         <v>47</v>
       </c>
       <c t="s" r="I88" s="7">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c t="s" r="J88" s="7">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="K88" s="7"/>
       <c r="L88" s="7"/>
@@ -4439,14 +4444,14 @@
         <v>13</v>
       </c>
       <c t="s" r="B89" s="7">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c t="s" r="C89" s="7">
         <v>14</v>
       </c>
       <c r="D89" s="7"/>
       <c t="s" r="E89" s="7">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F89" s="7">
         <v>321</v>
@@ -4455,20 +4460,20 @@
         <v>47</v>
       </c>
       <c t="s" r="H89" s="8">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c t="s" r="I89" s="7">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c t="s" r="J89" s="7">
+        <v>178</v>
+      </c>
+      <c t="s" r="K89" s="7">
         <v>177</v>
-      </c>
-      <c t="s" r="K89" s="7">
-        <v>176</v>
       </c>
       <c r="L89" s="7"/>
       <c t="s" r="M89" s="7">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="90" ht="15" customHeight="1">
@@ -4483,22 +4488,22 @@
       </c>
       <c r="D90" s="7"/>
       <c t="s" r="E90" s="7">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F90" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G90" s="8">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c t="s" r="H90" s="8">
         <v>47</v>
       </c>
       <c t="s" r="I90" s="7">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c t="s" r="J90" s="7">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="K90" s="7"/>
       <c r="L90" s="7"/>
@@ -4516,7 +4521,7 @@
       </c>
       <c r="D91" s="7"/>
       <c t="s" r="E91" s="7">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F91" s="7">
         <v>321</v>
@@ -4525,10 +4530,10 @@
         <v>47</v>
       </c>
       <c t="s" r="H91" s="8">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c t="s" r="I91" s="7">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c t="s" r="J91" s="7">
         <v>45</v>
@@ -4549,13 +4554,13 @@
       </c>
       <c r="D92" s="7"/>
       <c t="s" r="E92" s="7">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F92" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G92" s="8">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c t="s" r="H92" s="8">
         <v>47</v>
@@ -4564,7 +4569,7 @@
         <v>52</v>
       </c>
       <c t="s" r="J92" s="7">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="K92" s="7"/>
       <c r="L92" s="7"/>
@@ -4582,7 +4587,7 @@
       </c>
       <c r="D93" s="7"/>
       <c t="s" r="E93" s="7">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F93" s="7">
         <v>321</v>
@@ -4597,7 +4602,7 @@
         <v>50</v>
       </c>
       <c t="s" r="J93" s="7">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="K93" s="7"/>
       <c r="L93" s="7"/>
@@ -4630,13 +4635,13 @@
       </c>
       <c r="D95" s="7"/>
       <c t="s" r="E95" s="7">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F95" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G95" s="8">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c t="s" r="H95" s="8">
         <v>47</v>
@@ -4645,7 +4650,7 @@
         <v>39</v>
       </c>
       <c t="s" r="J95" s="7">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="K95" s="7"/>
       <c r="L95" s="7"/>
@@ -4663,7 +4668,7 @@
       </c>
       <c r="D96" s="7"/>
       <c t="s" r="E96" s="7">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F96" s="7">
         <v>321</v>
@@ -4675,10 +4680,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I96" s="7">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c t="s" r="J96" s="7">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="K96" s="7"/>
       <c r="L96" s="7"/>
@@ -4696,7 +4701,7 @@
       </c>
       <c r="D97" s="7"/>
       <c t="s" r="E97" s="7">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F97" s="7">
         <v>321</v>
@@ -4708,10 +4713,10 @@
         <v>47</v>
       </c>
       <c t="s" r="I97" s="7">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c t="s" r="J97" s="7">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="K97" s="7"/>
       <c r="L97" s="7"/>
@@ -4729,7 +4734,7 @@
       </c>
       <c r="D98" s="7"/>
       <c t="s" r="E98" s="7">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F98" s="7">
         <v>321</v>
@@ -4738,13 +4743,13 @@
         <v>47</v>
       </c>
       <c t="s" r="H98" s="8">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c t="s" r="I98" s="7">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c t="s" r="J98" s="7">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="K98" s="7"/>
       <c r="L98" s="7"/>
@@ -4762,22 +4767,22 @@
       </c>
       <c r="D99" s="7"/>
       <c t="s" r="E99" s="7">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F99" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G99" s="8">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c t="s" r="H99" s="8">
         <v>47</v>
       </c>
       <c t="s" r="I99" s="7">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c t="s" r="J99" s="7">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="K99" s="7"/>
       <c r="L99" s="7"/>
@@ -4810,22 +4815,22 @@
       </c>
       <c r="D101" s="7"/>
       <c t="s" r="E101" s="7">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F101" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G101" s="8">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c t="s" r="H101" s="8">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c t="s" r="I101" s="7">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c t="s" r="J101" s="7">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="K101" s="7"/>
       <c r="L101" s="7"/>
@@ -4843,19 +4848,19 @@
       </c>
       <c r="D102" s="7"/>
       <c t="s" r="E102" s="7">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F102" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G102" s="8">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c t="s" r="H102" s="8">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c t="s" r="I102" s="7">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c t="s" r="J102" s="7">
         <v>24</v>
@@ -4876,22 +4881,22 @@
       </c>
       <c r="D103" s="7"/>
       <c t="s" r="E103" s="7">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F103" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G103" s="8">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c t="s" r="H103" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I103" s="7">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c t="s" r="J103" s="7">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="K103" s="7"/>
       <c r="L103" s="7"/>
@@ -4909,7 +4914,7 @@
       </c>
       <c r="D104" s="7"/>
       <c t="s" r="E104" s="7">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F104" s="7">
         <v>321</v>
@@ -4918,13 +4923,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H104" s="8">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c t="s" r="I104" s="7">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c t="s" r="J104" s="7">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="K104" s="7"/>
       <c r="L104" s="7"/>
@@ -4942,22 +4947,22 @@
       </c>
       <c r="D105" s="7"/>
       <c t="s" r="E105" s="7">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F105" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G105" s="8">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c t="s" r="H105" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I105" s="7">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c t="s" r="J105" s="7">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="K105" s="7"/>
       <c r="L105" s="7"/>
@@ -4990,7 +4995,7 @@
       </c>
       <c r="D107" s="7"/>
       <c t="s" r="E107" s="7">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F107" s="7">
         <v>321</v>
@@ -5002,10 +5007,10 @@
         <v>47</v>
       </c>
       <c t="s" r="I107" s="7">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c t="s" r="J107" s="7">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="K107" s="7"/>
       <c r="L107" s="7"/>
@@ -5023,7 +5028,7 @@
       </c>
       <c r="D108" s="7"/>
       <c t="s" r="E108" s="7">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F108" s="7">
         <v>321</v>
@@ -5035,10 +5040,10 @@
         <v>66</v>
       </c>
       <c t="s" r="I108" s="7">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c t="s" r="J108" s="7">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K108" s="7"/>
       <c r="L108" s="7"/>
@@ -5056,7 +5061,7 @@
       </c>
       <c r="D109" s="7"/>
       <c t="s" r="E109" s="7">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F109" s="7">
         <v>321</v>
@@ -5071,7 +5076,7 @@
         <v>44</v>
       </c>
       <c t="s" r="J109" s="7">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="K109" s="7"/>
       <c r="L109" s="7"/>
@@ -5089,7 +5094,7 @@
       </c>
       <c r="D110" s="7"/>
       <c t="s" r="E110" s="7">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F110" s="7">
         <v>321</v>
@@ -5098,13 +5103,13 @@
         <v>47</v>
       </c>
       <c t="s" r="H110" s="8">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c t="s" r="I110" s="7">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c t="s" r="J110" s="7">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="K110" s="7"/>
       <c r="L110" s="7"/>
@@ -5122,22 +5127,22 @@
       </c>
       <c r="D111" s="7"/>
       <c t="s" r="E111" s="7">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F111" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G111" s="8">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c t="s" r="H111" s="8">
         <v>47</v>
       </c>
       <c t="s" r="I111" s="7">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c t="s" r="J111" s="7">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="K111" s="7"/>
       <c r="L111" s="7"/>
@@ -5170,7 +5175,7 @@
       </c>
       <c r="D113" s="7"/>
       <c t="s" r="E113" s="7">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="F113" s="7">
         <v>321</v>
@@ -5179,13 +5184,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H113" s="8">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c t="s" r="I113" s="7">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c t="s" r="J113" s="7">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="K113" s="7"/>
       <c r="L113" s="7"/>
@@ -5203,22 +5208,22 @@
       </c>
       <c r="D114" s="7"/>
       <c t="s" r="E114" s="7">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="F114" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G114" s="8">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c t="s" r="H114" s="8">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c t="s" r="I114" s="7">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c t="s" r="J114" s="7">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="K114" s="7"/>
       <c r="L114" s="7"/>
@@ -5236,22 +5241,22 @@
       </c>
       <c r="D115" s="7"/>
       <c t="s" r="E115" s="7">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="F115" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G115" s="8">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c t="s" r="H115" s="8">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c t="s" r="I115" s="7">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c t="s" r="J115" s="7">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="K115" s="7"/>
       <c r="L115" s="7"/>
@@ -5269,19 +5274,19 @@
       </c>
       <c r="D116" s="7"/>
       <c t="s" r="E116" s="7">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="F116" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G116" s="8">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c t="s" r="H116" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I116" s="7">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c t="s" r="J116" s="7">
         <v>40</v>
@@ -5302,7 +5307,7 @@
       </c>
       <c r="D117" s="7"/>
       <c t="s" r="E117" s="7">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="F117" s="7">
         <v>321</v>
@@ -5311,13 +5316,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H117" s="8">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c t="s" r="I117" s="7">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c t="s" r="J117" s="7">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="K117" s="7"/>
       <c r="L117" s="7"/>
@@ -5335,22 +5340,22 @@
       </c>
       <c r="D118" s="7"/>
       <c t="s" r="E118" s="7">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="F118" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G118" s="8">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c t="s" r="H118" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I118" s="7">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c t="s" r="J118" s="7">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="K118" s="7"/>
       <c r="L118" s="7"/>
@@ -5368,7 +5373,7 @@
       </c>
       <c r="D119" s="7"/>
       <c t="s" r="E119" s="7">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="F119" s="7">
         <v>321</v>
@@ -5377,13 +5382,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H119" s="8">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c t="s" r="I119" s="7">
         <v>25</v>
       </c>
       <c t="s" r="J119" s="7">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="K119" s="7"/>
       <c r="L119" s="7"/>
@@ -5401,22 +5406,22 @@
       </c>
       <c r="D120" s="7"/>
       <c t="s" r="E120" s="7">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="F120" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G120" s="8">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c t="s" r="H120" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I120" s="7">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c t="s" r="J120" s="7">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="K120" s="7"/>
       <c r="L120" s="7"/>
@@ -5449,7 +5454,7 @@
       </c>
       <c r="D122" s="7"/>
       <c t="s" r="E122" s="7">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="F122" s="7">
         <v>321</v>
@@ -5458,13 +5463,13 @@
         <v>47</v>
       </c>
       <c t="s" r="H122" s="8">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c t="s" r="I122" s="7">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c t="s" r="J122" s="7">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="K122" s="7"/>
       <c r="L122" s="7"/>
@@ -5482,22 +5487,22 @@
       </c>
       <c r="D123" s="7"/>
       <c t="s" r="E123" s="7">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="F123" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G123" s="8">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c t="s" r="H123" s="8">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c t="s" r="I123" s="7">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c t="s" r="J123" s="7">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="K123" s="7"/>
       <c r="L123" s="7"/>
@@ -5515,22 +5520,22 @@
       </c>
       <c r="D124" s="7"/>
       <c t="s" r="E124" s="7">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="F124" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G124" s="8">
+        <v>110</v>
+      </c>
+      <c t="s" r="H124" s="8">
+        <v>215</v>
+      </c>
+      <c t="s" r="I124" s="7">
         <v>109</v>
       </c>
-      <c t="s" r="H124" s="8">
-        <v>214</v>
-      </c>
-      <c t="s" r="I124" s="7">
-        <v>108</v>
-      </c>
       <c t="s" r="J124" s="7">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="K124" s="7"/>
       <c r="L124" s="7"/>
@@ -5548,22 +5553,22 @@
       </c>
       <c r="D125" s="7"/>
       <c t="s" r="E125" s="7">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="F125" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G125" s="8">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c t="s" r="H125" s="8">
         <v>47</v>
       </c>
       <c t="s" r="I125" s="7">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c t="s" r="J125" s="7">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="K125" s="7"/>
       <c r="L125" s="7"/>
@@ -5581,7 +5586,7 @@
       </c>
       <c r="D126" s="7"/>
       <c t="s" r="E126" s="7">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="F126" s="7">
         <v>321</v>
@@ -5593,10 +5598,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I126" s="7">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c t="s" r="J126" s="7">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="K126" s="7"/>
       <c r="L126" s="7"/>
@@ -5614,7 +5619,7 @@
       </c>
       <c r="D127" s="7"/>
       <c t="s" r="E127" s="7">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="F127" s="7">
         <v>321</v>
@@ -5629,7 +5634,7 @@
         <v>25</v>
       </c>
       <c t="s" r="J127" s="7">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="K127" s="7"/>
       <c r="L127" s="7"/>
@@ -5647,7 +5652,7 @@
       </c>
       <c r="D128" s="7"/>
       <c t="s" r="E128" s="7">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="F128" s="7">
         <v>321</v>
@@ -5659,10 +5664,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I128" s="7">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c t="s" r="J128" s="7">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="K128" s="7"/>
       <c r="L128" s="7"/>
@@ -5695,7 +5700,7 @@
       </c>
       <c r="D130" s="7"/>
       <c t="s" r="E130" s="7">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="F130" s="7">
         <v>321</v>
@@ -5707,10 +5712,10 @@
         <v>47</v>
       </c>
       <c t="s" r="I130" s="7">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c t="s" r="J130" s="7">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="K130" s="7"/>
       <c r="L130" s="7"/>
@@ -5728,7 +5733,7 @@
       </c>
       <c r="D131" s="7"/>
       <c t="s" r="E131" s="7">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="F131" s="7">
         <v>321</v>
@@ -5740,10 +5745,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I131" s="7">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c t="s" r="J131" s="7">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="K131" s="7"/>
       <c r="L131" s="7"/>
@@ -5761,7 +5766,7 @@
       </c>
       <c r="D132" s="7"/>
       <c t="s" r="E132" s="7">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="F132" s="7">
         <v>321</v>
@@ -5773,10 +5778,10 @@
         <v>65</v>
       </c>
       <c t="s" r="I132" s="7">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c t="s" r="J132" s="7">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K132" s="7"/>
       <c r="L132" s="7"/>
@@ -5794,7 +5799,7 @@
       </c>
       <c r="D133" s="7"/>
       <c t="s" r="E133" s="7">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="F133" s="7">
         <v>321</v>
@@ -5806,10 +5811,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I133" s="7">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c t="s" r="J133" s="7">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="K133" s="7"/>
       <c r="L133" s="7"/>
@@ -5842,7 +5847,7 @@
       </c>
       <c r="D135" s="7"/>
       <c t="s" r="E135" s="7">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="F135" s="7">
         <v>321</v>
@@ -5851,13 +5856,13 @@
         <v>47</v>
       </c>
       <c t="s" r="H135" s="8">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c t="s" r="I135" s="7">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c t="s" r="J135" s="7">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="K135" s="7"/>
       <c r="L135" s="7"/>
@@ -5875,13 +5880,13 @@
       </c>
       <c r="D136" s="7"/>
       <c t="s" r="E136" s="7">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="F136" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G136" s="8">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c t="s" r="H136" s="8">
         <v>47</v>
@@ -5890,7 +5895,7 @@
         <v>39</v>
       </c>
       <c t="s" r="J136" s="7">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="K136" s="7"/>
       <c r="L136" s="7"/>
@@ -5908,7 +5913,7 @@
       </c>
       <c r="D137" s="7"/>
       <c t="s" r="E137" s="7">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="F137" s="7">
         <v>321</v>
@@ -5917,10 +5922,10 @@
         <v>47</v>
       </c>
       <c t="s" r="H137" s="8">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c t="s" r="I137" s="7">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c t="s" r="J137" s="7">
         <v>20</v>
@@ -5941,22 +5946,22 @@
       </c>
       <c r="D138" s="7"/>
       <c t="s" r="E138" s="7">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="F138" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G138" s="8">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c t="s" r="H138" s="8">
         <v>66</v>
       </c>
       <c t="s" r="I138" s="7">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c t="s" r="J138" s="7">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="K138" s="7"/>
       <c r="L138" s="7"/>
@@ -5974,7 +5979,7 @@
       </c>
       <c r="D139" s="7"/>
       <c t="s" r="E139" s="7">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="F139" s="7">
         <v>321</v>
@@ -5983,13 +5988,13 @@
         <v>66</v>
       </c>
       <c t="s" r="H139" s="8">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c t="s" r="I139" s="7">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c t="s" r="J139" s="7">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="K139" s="7"/>
       <c r="L139" s="7"/>
@@ -6007,22 +6012,22 @@
       </c>
       <c r="D140" s="7"/>
       <c t="s" r="E140" s="7">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="F140" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G140" s="8">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c t="s" r="H140" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I140" s="7">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c t="s" r="J140" s="7">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="K140" s="7"/>
       <c r="L140" s="7"/>
@@ -6040,7 +6045,7 @@
       </c>
       <c r="D141" s="7"/>
       <c t="s" r="E141" s="7">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="F141" s="7">
         <v>321</v>
@@ -6049,16 +6054,16 @@
         <v>16</v>
       </c>
       <c t="s" r="H141" s="8">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c t="s" r="I141" s="7">
         <v>27</v>
       </c>
       <c t="s" r="J141" s="7">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c t="s" r="K141" s="7">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="L141" s="7"/>
       <c t="s" r="M141" s="7">
@@ -6092,7 +6097,7 @@
       </c>
       <c r="D143" s="7"/>
       <c t="s" r="E143" s="7">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F143" s="7">
         <v>321</v>
@@ -6101,13 +6106,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H143" s="8">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c t="s" r="I143" s="7">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c t="s" r="J143" s="7">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="K143" s="7"/>
       <c r="L143" s="7"/>
@@ -6125,22 +6130,22 @@
       </c>
       <c r="D144" s="7"/>
       <c t="s" r="E144" s="7">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F144" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G144" s="8">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c t="s" r="H144" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I144" s="7">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c t="s" r="J144" s="7">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="K144" s="7"/>
       <c r="L144" s="7"/>
@@ -6151,14 +6156,14 @@
         <v>13</v>
       </c>
       <c t="s" r="B145" s="7">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c t="s" r="C145" s="7">
         <v>14</v>
       </c>
       <c r="D145" s="7"/>
       <c t="s" r="E145" s="7">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F145" s="7">
         <v>321</v>
@@ -6167,20 +6172,20 @@
         <v>16</v>
       </c>
       <c t="s" r="H145" s="8">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c t="s" r="I145" s="7">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c t="s" r="J145" s="7">
+        <v>235</v>
+      </c>
+      <c t="s" r="K145" s="7">
         <v>234</v>
-      </c>
-      <c t="s" r="K145" s="7">
-        <v>233</v>
       </c>
       <c r="L145" s="7"/>
       <c t="s" r="M145" s="7">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="146" ht="14.25" customHeight="1">
@@ -6188,36 +6193,36 @@
         <v>13</v>
       </c>
       <c t="s" r="B146" s="7">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c t="s" r="C146" s="7">
         <v>14</v>
       </c>
       <c r="D146" s="7"/>
       <c t="s" r="E146" s="7">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F146" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G146" s="8">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c t="s" r="H146" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I146" s="7">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c t="s" r="J146" s="7">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c t="s" r="K146" s="7">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L146" s="7"/>
       <c t="s" r="M146" s="7">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="147" ht="14.25" customHeight="1">
@@ -6225,14 +6230,14 @@
         <v>13</v>
       </c>
       <c t="s" r="B147" s="7">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c t="s" r="C147" s="7">
         <v>14</v>
       </c>
       <c r="D147" s="7"/>
       <c t="s" r="E147" s="7">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F147" s="7">
         <v>321</v>
@@ -6241,20 +6246,20 @@
         <v>16</v>
       </c>
       <c t="s" r="H147" s="8">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c t="s" r="I147" s="7">
+        <v>84</v>
+      </c>
+      <c t="s" r="J147" s="7">
         <v>83</v>
       </c>
-      <c t="s" r="J147" s="7">
-        <v>82</v>
-      </c>
       <c t="s" r="K147" s="7">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="L147" s="7"/>
       <c t="s" r="M147" s="7">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="148" ht="14.25" customHeight="1">
@@ -6262,36 +6267,36 @@
         <v>13</v>
       </c>
       <c t="s" r="B148" s="7">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c t="s" r="C148" s="7">
         <v>14</v>
       </c>
       <c r="D148" s="7"/>
       <c t="s" r="E148" s="7">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F148" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G148" s="8">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c t="s" r="H148" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I148" s="7">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c t="s" r="J148" s="7">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c t="s" r="K148" s="7">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="L148" s="7"/>
       <c t="s" r="M148" s="7">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="149" ht="14.25" customHeight="1">
@@ -6306,7 +6311,7 @@
       </c>
       <c r="D149" s="7"/>
       <c t="s" r="E149" s="7">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F149" s="7">
         <v>321</v>
@@ -6318,10 +6323,10 @@
         <v>47</v>
       </c>
       <c t="s" r="I149" s="7">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c t="s" r="J149" s="7">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="K149" s="7"/>
       <c r="L149" s="7"/>
@@ -6350,26 +6355,26 @@
         <v>7707</v>
       </c>
       <c t="s" r="C151" s="7">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="D151" s="7"/>
       <c t="s" r="E151" s="7">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F151" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G151" s="8">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c t="s" r="H151" s="8">
         <v>47</v>
       </c>
       <c t="s" r="I151" s="7">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c t="s" r="J151" s="7">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="K151" s="7"/>
       <c r="L151" s="7"/>
@@ -6383,11 +6388,11 @@
         <v>7707</v>
       </c>
       <c t="s" r="C152" s="7">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="D152" s="7"/>
       <c t="s" r="E152" s="7">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F152" s="7">
         <v>321</v>
@@ -6396,10 +6401,10 @@
         <v>47</v>
       </c>
       <c t="s" r="H152" s="8">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c t="s" r="I152" s="7">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c t="s" r="J152" s="7">
         <v>21</v>
@@ -6420,22 +6425,22 @@
       </c>
       <c r="D153" s="7"/>
       <c t="s" r="E153" s="7">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F153" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G153" s="8">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c t="s" r="H153" s="8">
         <v>47</v>
       </c>
       <c t="s" r="I153" s="7">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c t="s" r="J153" s="7">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="K153" s="7"/>
       <c r="L153" s="7"/>
@@ -6453,7 +6458,7 @@
       </c>
       <c r="D154" s="7"/>
       <c t="s" r="E154" s="7">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F154" s="7">
         <v>321</v>
@@ -6462,13 +6467,13 @@
         <v>47</v>
       </c>
       <c t="s" r="H154" s="8">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c t="s" r="I154" s="7">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c t="s" r="J154" s="7">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="K154" s="7"/>
       <c r="L154" s="7"/>
@@ -6501,7 +6506,7 @@
       </c>
       <c r="D156" s="7"/>
       <c t="s" r="E156" s="7">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="F156" s="7">
         <v>321</v>
@@ -6513,10 +6518,10 @@
         <v>66</v>
       </c>
       <c t="s" r="I156" s="7">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c t="s" r="J156" s="7">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="K156" s="7"/>
       <c r="L156" s="7"/>
@@ -6534,7 +6539,7 @@
       </c>
       <c r="D157" s="7"/>
       <c t="s" r="E157" s="7">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="F157" s="7">
         <v>321</v>
@@ -6546,7 +6551,7 @@
         <v>47</v>
       </c>
       <c t="s" r="I157" s="7">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c t="s" r="J157" s="7">
         <v>20</v>
@@ -6567,7 +6572,7 @@
       </c>
       <c r="D158" s="7"/>
       <c t="s" r="E158" s="7">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="F158" s="7">
         <v>321</v>
@@ -6576,10 +6581,10 @@
         <v>47</v>
       </c>
       <c t="s" r="H158" s="8">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c t="s" r="I158" s="7">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c t="s" r="J158" s="7">
         <v>48</v>
@@ -6600,13 +6605,13 @@
       </c>
       <c r="D159" s="7"/>
       <c t="s" r="E159" s="7">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="F159" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G159" s="8">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c t="s" r="H159" s="8">
         <v>47</v>
@@ -6615,7 +6620,7 @@
         <v>44</v>
       </c>
       <c t="s" r="J159" s="7">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="K159" s="7"/>
       <c r="L159" s="7"/>
@@ -6633,7 +6638,7 @@
       </c>
       <c r="D160" s="7"/>
       <c t="s" r="E160" s="7">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="F160" s="7">
         <v>321</v>
@@ -6642,13 +6647,13 @@
         <v>47</v>
       </c>
       <c t="s" r="H160" s="8">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c t="s" r="I160" s="7">
         <v>25</v>
       </c>
       <c t="s" r="J160" s="7">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="K160" s="7"/>
       <c r="L160" s="7"/>
@@ -6666,22 +6671,22 @@
       </c>
       <c r="D161" s="7"/>
       <c t="s" r="E161" s="7">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="F161" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G161" s="8">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c t="s" r="H161" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I161" s="7">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c t="s" r="J161" s="7">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="K161" s="7"/>
       <c r="L161" s="7"/>
@@ -6710,11 +6715,11 @@
         <v>5069</v>
       </c>
       <c t="s" r="C163" s="7">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="D163" s="7"/>
       <c t="s" r="E163" s="7">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="F163" s="7">
         <v>321</v>
@@ -6723,10 +6728,10 @@
         <v>47</v>
       </c>
       <c t="s" r="H163" s="8">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c t="s" r="I163" s="7">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c t="s" r="J163" s="7">
         <v>55</v>
@@ -6743,26 +6748,26 @@
         <v>1605</v>
       </c>
       <c t="s" r="C164" s="7">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D164" s="7"/>
       <c t="s" r="E164" s="7">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="F164" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G164" s="8">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c t="s" r="H164" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I164" s="7">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c t="s" r="J164" s="7">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="K164" s="7"/>
       <c r="L164" s="7"/>
@@ -6780,7 +6785,7 @@
       </c>
       <c r="D165" s="7"/>
       <c t="s" r="E165" s="7">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="F165" s="7">
         <v>321</v>
@@ -6789,13 +6794,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H165" s="8">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c t="s" r="I165" s="7">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c t="s" r="J165" s="7">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="K165" s="7"/>
       <c r="L165" s="7"/>
@@ -6813,22 +6818,22 @@
       </c>
       <c r="D166" s="7"/>
       <c t="s" r="E166" s="7">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="F166" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G166" s="8">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c t="s" r="H166" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I166" s="7">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c t="s" r="J166" s="7">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="K166" s="7"/>
       <c r="L166" s="7"/>
@@ -6846,7 +6851,7 @@
       </c>
       <c r="D167" s="7"/>
       <c t="s" r="E167" s="7">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="F167" s="7">
         <v>321</v>
@@ -6855,7 +6860,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H167" s="8">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c t="s" r="I167" s="7">
         <v>44</v>
@@ -6879,22 +6884,22 @@
       </c>
       <c r="D168" s="7"/>
       <c t="s" r="E168" s="7">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="F168" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G168" s="8">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c t="s" r="H168" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I168" s="7">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c t="s" r="J168" s="7">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="K168" s="7"/>
       <c r="L168" s="7"/>
@@ -6927,22 +6932,22 @@
       </c>
       <c r="D170" s="7"/>
       <c t="s" r="E170" s="7">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="F170" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G170" s="8">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c t="s" r="H170" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I170" s="7">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c t="s" r="J170" s="7">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="K170" s="7"/>
       <c r="L170" s="7"/>
@@ -6960,7 +6965,7 @@
       </c>
       <c r="D171" s="7"/>
       <c t="s" r="E171" s="7">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="F171" s="7">
         <v>321</v>
@@ -6969,13 +6974,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H171" s="8">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c t="s" r="I171" s="7">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c t="s" r="J171" s="7">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="K171" s="7"/>
       <c r="L171" s="7"/>
@@ -6993,22 +6998,22 @@
       </c>
       <c r="D172" s="7"/>
       <c t="s" r="E172" s="7">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="F172" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G172" s="8">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c t="s" r="H172" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I172" s="7">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c t="s" r="J172" s="7">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="K172" s="7"/>
       <c r="L172" s="7"/>
@@ -7026,7 +7031,7 @@
       </c>
       <c r="D173" s="7"/>
       <c t="s" r="E173" s="7">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="F173" s="7">
         <v>321</v>
@@ -7035,13 +7040,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H173" s="8">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c t="s" r="I173" s="7">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c t="s" r="J173" s="7">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="K173" s="7"/>
       <c r="L173" s="7"/>
@@ -7074,22 +7079,22 @@
       </c>
       <c r="D175" s="7"/>
       <c t="s" r="E175" s="7">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="F175" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G175" s="8">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c t="s" r="H175" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I175" s="7">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c t="s" r="J175" s="7">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K175" s="7"/>
       <c r="L175" s="7"/>
@@ -7107,7 +7112,7 @@
       </c>
       <c r="D176" s="7"/>
       <c t="s" r="E176" s="7">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="F176" s="7">
         <v>321</v>
@@ -7116,13 +7121,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H176" s="8">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c t="s" r="I176" s="7">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c t="s" r="J176" s="7">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="K176" s="7"/>
       <c r="L176" s="7"/>
@@ -7140,19 +7145,19 @@
       </c>
       <c r="D177" s="7"/>
       <c t="s" r="E177" s="7">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="F177" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G177" s="8">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c t="s" r="H177" s="8">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c t="s" r="I177" s="7">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c t="s" r="J177" s="7">
         <v>49</v>
@@ -7173,22 +7178,22 @@
       </c>
       <c r="D178" s="7"/>
       <c t="s" r="E178" s="7">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="F178" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G178" s="8">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c t="s" r="H178" s="8">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c t="s" r="I178" s="7">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c t="s" r="J178" s="7">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K178" s="7"/>
       <c r="L178" s="7"/>
@@ -7221,7 +7226,7 @@
       </c>
       <c r="D180" s="7"/>
       <c t="s" r="E180" s="7">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="F180" s="7">
         <v>321</v>
@@ -7230,13 +7235,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H180" s="8">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c t="s" r="I180" s="7">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c t="s" r="J180" s="7">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="K180" s="7"/>
       <c r="L180" s="7"/>
@@ -7254,13 +7259,13 @@
       </c>
       <c r="D181" s="7"/>
       <c t="s" r="E181" s="7">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="F181" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G181" s="8">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c t="s" r="H181" s="8">
         <v>16</v>
@@ -7269,7 +7274,7 @@
         <v>63</v>
       </c>
       <c t="s" r="J181" s="7">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="K181" s="7"/>
       <c r="L181" s="7"/>
@@ -7280,14 +7285,14 @@
         <v>13</v>
       </c>
       <c t="s" r="B182" s="7">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c t="s" r="C182" s="7">
         <v>14</v>
       </c>
       <c r="D182" s="7"/>
       <c t="s" r="E182" s="7">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="F182" s="7">
         <v>321</v>
@@ -7296,16 +7301,16 @@
         <v>16</v>
       </c>
       <c t="s" r="H182" s="8">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c t="s" r="I182" s="7">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c t="s" r="J182" s="7">
         <v>42</v>
       </c>
       <c t="s" r="K182" s="7">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="L182" s="7"/>
       <c t="s" r="M182" s="7">
@@ -7317,32 +7322,32 @@
         <v>13</v>
       </c>
       <c t="s" r="B183" s="7">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c t="s" r="C183" s="7">
         <v>14</v>
       </c>
       <c r="D183" s="7"/>
       <c t="s" r="E183" s="7">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="F183" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G183" s="8">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c t="s" r="H183" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I183" s="7">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c t="s" r="J183" s="7">
         <v>48</v>
       </c>
       <c t="s" r="K183" s="7">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="L183" s="7"/>
       <c t="s" r="M183" s="7">
@@ -7354,14 +7359,14 @@
         <v>13</v>
       </c>
       <c t="s" r="B184" s="7">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c t="s" r="C184" s="7">
         <v>14</v>
       </c>
       <c r="D184" s="7"/>
       <c t="s" r="E184" s="7">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="F184" s="7">
         <v>321</v>
@@ -7370,7 +7375,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H184" s="8">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c t="s" r="I184" s="7">
         <v>21</v>
@@ -7391,32 +7396,32 @@
         <v>13</v>
       </c>
       <c t="s" r="B185" s="7">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c t="s" r="C185" s="7">
         <v>14</v>
       </c>
       <c r="D185" s="7"/>
       <c t="s" r="E185" s="7">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="F185" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G185" s="8">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c t="s" r="H185" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I185" s="7">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c t="s" r="J185" s="7">
         <v>53</v>
       </c>
       <c t="s" r="K185" s="7">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="L185" s="7"/>
       <c t="s" r="M185" s="7">
@@ -7435,7 +7440,7 @@
       </c>
       <c r="D186" s="7"/>
       <c t="s" r="E186" s="7">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="F186" s="7">
         <v>321</v>
@@ -7447,10 +7452,10 @@
         <v>47</v>
       </c>
       <c t="s" r="I186" s="7">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c t="s" r="J186" s="7">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="K186" s="7"/>
       <c r="L186" s="7"/>
@@ -7483,7 +7488,7 @@
       </c>
       <c r="D188" s="7"/>
       <c t="s" r="E188" s="7">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="F188" s="7">
         <v>321</v>
@@ -7495,10 +7500,10 @@
         <v>47</v>
       </c>
       <c t="s" r="I188" s="7">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c t="s" r="J188" s="7">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="K188" s="7"/>
       <c r="L188" s="7"/>
@@ -7516,7 +7521,7 @@
       </c>
       <c r="D189" s="7"/>
       <c t="s" r="E189" s="7">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="F189" s="7">
         <v>321</v>
@@ -7525,13 +7530,13 @@
         <v>47</v>
       </c>
       <c t="s" r="H189" s="8">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c t="s" r="I189" s="7">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c t="s" r="J189" s="7">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="K189" s="7"/>
       <c r="L189" s="7"/>
@@ -7549,22 +7554,22 @@
       </c>
       <c r="D190" s="7"/>
       <c t="s" r="E190" s="7">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="F190" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G190" s="8">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c t="s" r="H190" s="8">
         <v>47</v>
       </c>
       <c t="s" r="I190" s="7">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c t="s" r="J190" s="7">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="K190" s="7"/>
       <c r="L190" s="7"/>
@@ -7582,7 +7587,7 @@
       </c>
       <c r="D191" s="7"/>
       <c t="s" r="E191" s="7">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="F191" s="7">
         <v>321</v>
@@ -7594,10 +7599,10 @@
         <v>65</v>
       </c>
       <c t="s" r="I191" s="7">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c t="s" r="J191" s="7">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="K191" s="7"/>
       <c r="L191" s="7"/>
@@ -7630,7 +7635,7 @@
       </c>
       <c r="D193" s="7"/>
       <c t="s" r="E193" s="7">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="F193" s="7">
         <v>321</v>
@@ -7639,13 +7644,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H193" s="8">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c t="s" r="I193" s="7">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c t="s" r="J193" s="7">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="K193" s="7"/>
       <c r="L193" s="7"/>
@@ -7663,22 +7668,22 @@
       </c>
       <c r="D194" s="7"/>
       <c t="s" r="E194" s="7">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="F194" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G194" s="8">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c t="s" r="H194" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I194" s="7">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c t="s" r="J194" s="7">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="K194" s="7"/>
       <c r="L194" s="7"/>
@@ -7696,7 +7701,7 @@
       </c>
       <c r="D195" s="7"/>
       <c t="s" r="E195" s="7">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="F195" s="7">
         <v>321</v>
@@ -7708,10 +7713,10 @@
         <v>66</v>
       </c>
       <c t="s" r="I195" s="7">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c t="s" r="J195" s="7">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="K195" s="7"/>
       <c r="L195" s="7"/>
@@ -7729,7 +7734,7 @@
       </c>
       <c r="D196" s="7"/>
       <c t="s" r="E196" s="7">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="F196" s="7">
         <v>321</v>
@@ -7744,7 +7749,7 @@
         <v>40</v>
       </c>
       <c t="s" r="J196" s="7">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="K196" s="7"/>
       <c r="L196" s="7"/>
@@ -7762,7 +7767,7 @@
       </c>
       <c r="D197" s="7"/>
       <c t="s" r="E197" s="7">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="F197" s="7">
         <v>321</v>
@@ -7771,10 +7776,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H197" s="8">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c t="s" r="I197" s="7">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c t="s" r="J197" s="7">
         <v>44</v>
@@ -7795,19 +7800,19 @@
       </c>
       <c r="D198" s="7"/>
       <c t="s" r="E198" s="7">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="F198" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G198" s="8">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c t="s" r="H198" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I198" s="7">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c t="s" r="J198" s="7">
         <v>25</v>
@@ -7821,14 +7826,14 @@
         <v>13</v>
       </c>
       <c t="s" r="B199" s="7">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c t="s" r="C199" s="7">
         <v>14</v>
       </c>
       <c r="D199" s="7"/>
       <c t="s" r="E199" s="7">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="F199" s="7">
         <v>321</v>
@@ -7843,14 +7848,14 @@
         <v>27</v>
       </c>
       <c t="s" r="J199" s="7">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c t="s" r="K199" s="7">
         <v>27</v>
       </c>
       <c r="L199" s="7"/>
       <c t="s" r="M199" s="7">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="200" ht="15" customHeight="1">
@@ -7880,22 +7885,22 @@
       </c>
       <c r="D201" s="7"/>
       <c t="s" r="E201" s="7">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="F201" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G201" s="8">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c t="s" r="H201" s="8">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c t="s" r="I201" s="7">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c t="s" r="J201" s="7">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="K201" s="7"/>
       <c r="L201" s="7"/>
@@ -7913,22 +7918,22 @@
       </c>
       <c r="D202" s="7"/>
       <c t="s" r="E202" s="7">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="F202" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G202" s="8">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c t="s" r="H202" s="8">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c t="s" r="I202" s="7">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c t="s" r="J202" s="7">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="K202" s="7"/>
       <c r="L202" s="7"/>
@@ -7946,22 +7951,22 @@
       </c>
       <c r="D203" s="7"/>
       <c t="s" r="E203" s="7">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="F203" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G203" s="8">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c t="s" r="H203" s="8">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c t="s" r="I203" s="7">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c t="s" r="J203" s="7">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="K203" s="7"/>
       <c r="L203" s="7"/>
@@ -7979,22 +7984,22 @@
       </c>
       <c r="D204" s="7"/>
       <c t="s" r="E204" s="7">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="F204" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G204" s="8">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c t="s" r="H204" s="8">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c t="s" r="I204" s="7">
         <v>45</v>
       </c>
       <c t="s" r="J204" s="7">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="K204" s="7"/>
       <c r="L204" s="7"/>
@@ -8012,22 +8017,22 @@
       </c>
       <c r="D205" s="7"/>
       <c t="s" r="E205" s="7">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="F205" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G205" s="8">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c t="s" r="H205" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I205" s="7">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c t="s" r="J205" s="7">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="K205" s="7"/>
       <c r="L205" s="7"/>
@@ -8045,7 +8050,7 @@
       </c>
       <c r="D206" s="7"/>
       <c t="s" r="E206" s="7">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="F206" s="7">
         <v>321</v>
@@ -8054,13 +8059,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H206" s="8">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c t="s" r="I206" s="7">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c t="s" r="J206" s="7">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="K206" s="7"/>
       <c r="L206" s="7"/>
@@ -8093,7 +8098,7 @@
       </c>
       <c r="D208" s="7"/>
       <c t="s" r="E208" s="7">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="F208" s="7">
         <v>321</v>
@@ -8105,10 +8110,10 @@
         <v>23</v>
       </c>
       <c t="s" r="I208" s="7">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c t="s" r="J208" s="7">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K208" s="7"/>
       <c r="L208" s="7"/>
@@ -8126,7 +8131,7 @@
       </c>
       <c r="D209" s="7"/>
       <c t="s" r="E209" s="7">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="F209" s="7">
         <v>321</v>
@@ -8138,7 +8143,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I209" s="7">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c t="s" r="J209" s="7">
         <v>39</v>
@@ -8159,7 +8164,7 @@
       </c>
       <c r="D210" s="7"/>
       <c t="s" r="E210" s="7">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="F210" s="7">
         <v>321</v>
@@ -8168,13 +8173,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H210" s="8">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c t="s" r="I210" s="7">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c t="s" r="J210" s="7">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="K210" s="7"/>
       <c r="L210" s="7"/>
@@ -8192,22 +8197,22 @@
       </c>
       <c r="D211" s="7"/>
       <c t="s" r="E211" s="7">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="F211" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G211" s="8">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c t="s" r="H211" s="8">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c t="s" r="I211" s="7">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c t="s" r="J211" s="7">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="K211" s="7"/>
       <c r="L211" s="7"/>
@@ -8225,22 +8230,22 @@
       </c>
       <c r="D212" s="7"/>
       <c t="s" r="E212" s="7">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="F212" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G212" s="8">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c t="s" r="H212" s="8">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c t="s" r="I212" s="7">
         <v>48</v>
       </c>
       <c t="s" r="J212" s="7">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="K212" s="7"/>
       <c r="L212" s="7"/>
@@ -8251,36 +8256,36 @@
         <v>13</v>
       </c>
       <c t="s" r="B213" s="7">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c t="s" r="C213" s="7">
         <v>14</v>
       </c>
       <c r="D213" s="7"/>
       <c t="s" r="E213" s="7">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="F213" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G213" s="8">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c t="s" r="H213" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I213" s="7">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c t="s" r="J213" s="7">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c t="s" r="K213" s="7">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="L213" s="7"/>
       <c t="s" r="M213" s="7">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="214" ht="14.25" customHeight="1">
@@ -8288,14 +8293,14 @@
         <v>13</v>
       </c>
       <c t="s" r="B214" s="7">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c t="s" r="C214" s="7">
         <v>14</v>
       </c>
       <c r="D214" s="7"/>
       <c t="s" r="E214" s="7">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="F214" s="7">
         <v>321</v>
@@ -8304,20 +8309,20 @@
         <v>16</v>
       </c>
       <c t="s" r="H214" s="8">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c t="s" r="I214" s="7">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c t="s" r="J214" s="7">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c t="s" r="K214" s="7">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="L214" s="7"/>
       <c t="s" r="M214" s="7">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="215" ht="15" customHeight="1">
@@ -8347,7 +8352,7 @@
       </c>
       <c r="D216" s="7"/>
       <c t="s" r="E216" s="7">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="F216" s="7">
         <v>321</v>
@@ -8359,10 +8364,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I216" s="7">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c t="s" r="J216" s="7">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="K216" s="7"/>
       <c r="L216" s="7"/>
@@ -8380,7 +8385,7 @@
       </c>
       <c r="D217" s="7"/>
       <c t="s" r="E217" s="7">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="F217" s="7">
         <v>321</v>
@@ -8389,13 +8394,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H217" s="8">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c t="s" r="I217" s="7">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c t="s" r="J217" s="7">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="K217" s="7"/>
       <c r="L217" s="7"/>
@@ -8413,22 +8418,22 @@
       </c>
       <c r="D218" s="7"/>
       <c t="s" r="E218" s="7">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="F218" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G218" s="8">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c t="s" r="H218" s="8">
         <v>66</v>
       </c>
       <c t="s" r="I218" s="7">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c t="s" r="J218" s="7">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="K218" s="7"/>
       <c r="L218" s="7"/>
@@ -8446,7 +8451,7 @@
       </c>
       <c r="D219" s="7"/>
       <c t="s" r="E219" s="7">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="F219" s="7">
         <v>321</v>
@@ -8455,13 +8460,13 @@
         <v>66</v>
       </c>
       <c t="s" r="H219" s="8">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c t="s" r="I219" s="7">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c t="s" r="J219" s="7">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="K219" s="7"/>
       <c r="L219" s="7"/>
@@ -8479,19 +8484,19 @@
       </c>
       <c r="D220" s="7"/>
       <c t="s" r="E220" s="7">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="F220" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G220" s="8">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c t="s" r="H220" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I220" s="7">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c t="s" r="J220" s="7">
         <v>60</v>
@@ -8527,7 +8532,7 @@
       </c>
       <c r="D222" s="7"/>
       <c t="s" r="E222" s="7">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="F222" s="7">
         <v>321</v>
@@ -8536,13 +8541,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H222" s="8">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c t="s" r="I222" s="7">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c t="s" r="J222" s="7">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="K222" s="7"/>
       <c r="L222" s="7"/>
@@ -8560,22 +8565,22 @@
       </c>
       <c r="D223" s="7"/>
       <c t="s" r="E223" s="7">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="F223" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G223" s="8">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c t="s" r="H223" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I223" s="7">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c t="s" r="J223" s="7">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="K223" s="7"/>
       <c r="L223" s="7"/>
@@ -8586,14 +8591,14 @@
         <v>13</v>
       </c>
       <c t="s" r="B224" s="7">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c t="s" r="C224" s="7">
         <v>14</v>
       </c>
       <c r="D224" s="7"/>
       <c t="s" r="E224" s="7">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="F224" s="7">
         <v>321</v>
@@ -8602,20 +8607,20 @@
         <v>16</v>
       </c>
       <c t="s" r="H224" s="8">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c t="s" r="I224" s="7">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c t="s" r="J224" s="7">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c t="s" r="K224" s="7">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="L224" s="7"/>
       <c t="s" r="M224" s="7">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="225" ht="15" customHeight="1">
@@ -8623,32 +8628,32 @@
         <v>13</v>
       </c>
       <c t="s" r="B225" s="7">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c t="s" r="C225" s="7">
         <v>14</v>
       </c>
       <c r="D225" s="7"/>
       <c t="s" r="E225" s="7">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="F225" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G225" s="8">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c t="s" r="H225" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I225" s="7">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c t="s" r="J225" s="7">
         <v>59</v>
       </c>
       <c t="s" r="K225" s="7">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="L225" s="7"/>
       <c t="s" r="M225" s="7">
@@ -8660,14 +8665,14 @@
         <v>13</v>
       </c>
       <c t="s" r="B226" s="7">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c t="s" r="C226" s="7">
         <v>14</v>
       </c>
       <c r="D226" s="7"/>
       <c t="s" r="E226" s="7">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="F226" s="7">
         <v>321</v>
@@ -8676,20 +8681,20 @@
         <v>16</v>
       </c>
       <c t="s" r="H226" s="8">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c t="s" r="I226" s="7">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c t="s" r="J226" s="7">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c t="s" r="K226" s="7">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="L226" s="7"/>
       <c t="s" r="M226" s="7">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="227" ht="14.25" customHeight="1">
@@ -8697,36 +8702,36 @@
         <v>13</v>
       </c>
       <c t="s" r="B227" s="7">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c t="s" r="C227" s="7">
         <v>14</v>
       </c>
       <c r="D227" s="7"/>
       <c t="s" r="E227" s="7">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="F227" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G227" s="8">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c t="s" r="H227" s="8">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c t="s" r="I227" s="7">
         <v>27</v>
       </c>
       <c t="s" r="J227" s="7">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c t="s" r="K227" s="7">
         <v>27</v>
       </c>
       <c r="L227" s="7"/>
       <c t="s" r="M227" s="7">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="228" ht="14.25" customHeight="1">
@@ -8734,36 +8739,36 @@
         <v>13</v>
       </c>
       <c t="s" r="B228" s="7">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c t="s" r="C228" s="7">
         <v>14</v>
       </c>
       <c r="D228" s="7"/>
       <c t="s" r="E228" s="7">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="F228" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G228" s="8">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c t="s" r="H228" s="8">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c t="s" r="I228" s="7">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c t="s" r="J228" s="7">
+        <v>312</v>
+      </c>
+      <c t="s" r="K228" s="7">
         <v>311</v>
-      </c>
-      <c t="s" r="K228" s="7">
-        <v>310</v>
       </c>
       <c r="L228" s="7"/>
       <c t="s" r="M228" s="7">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="229" ht="14.25" customHeight="1">
@@ -8778,22 +8783,22 @@
       </c>
       <c r="D229" s="7"/>
       <c t="s" r="E229" s="7">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="F229" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G229" s="8">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c t="s" r="H229" s="8">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c t="s" r="I229" s="7">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c t="s" r="J229" s="7">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="K229" s="7"/>
       <c r="L229" s="7"/>
@@ -8826,7 +8831,7 @@
       </c>
       <c r="D231" s="7"/>
       <c t="s" r="E231" s="7">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="F231" s="7">
         <v>321</v>
@@ -8838,10 +8843,10 @@
         <v>47</v>
       </c>
       <c t="s" r="I231" s="7">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c t="s" r="J231" s="7">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="K231" s="7"/>
       <c r="L231" s="7"/>
@@ -8859,7 +8864,7 @@
       </c>
       <c r="D232" s="7"/>
       <c t="s" r="E232" s="7">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="F232" s="7">
         <v>321</v>
@@ -8871,10 +8876,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I232" s="7">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c t="s" r="J232" s="7">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="K232" s="7"/>
       <c r="L232" s="7"/>
@@ -8885,14 +8890,14 @@
         <v>13</v>
       </c>
       <c t="s" r="B233" s="7">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c t="s" r="C233" s="7">
         <v>14</v>
       </c>
       <c r="D233" s="7"/>
       <c t="s" r="E233" s="7">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="F233" s="7">
         <v>321</v>
@@ -8904,17 +8909,17 @@
         <v>47</v>
       </c>
       <c t="s" r="I233" s="7">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c t="s" r="J233" s="7">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c t="s" r="K233" s="7">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="L233" s="7"/>
       <c t="s" r="M233" s="7">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="234" ht="14.25" customHeight="1">
@@ -8929,7 +8934,7 @@
       </c>
       <c r="D234" s="7"/>
       <c t="s" r="E234" s="7">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="F234" s="7">
         <v>321</v>
@@ -8938,10 +8943,10 @@
         <v>47</v>
       </c>
       <c t="s" r="H234" s="8">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c t="s" r="I234" s="7">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c t="s" r="J234" s="7">
         <v>24</v>
@@ -8962,22 +8967,22 @@
       </c>
       <c r="D235" s="7"/>
       <c t="s" r="E235" s="7">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="F235" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G235" s="8">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c t="s" r="H235" s="8">
         <v>47</v>
       </c>
       <c t="s" r="I235" s="7">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c t="s" r="J235" s="7">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="K235" s="7"/>
       <c r="L235" s="7"/>
@@ -8995,7 +9000,7 @@
       </c>
       <c r="D236" s="7"/>
       <c t="s" r="E236" s="7">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="F236" s="7">
         <v>321</v>
@@ -9007,10 +9012,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I236" s="7">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c t="s" r="J236" s="7">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="K236" s="7"/>
       <c r="L236" s="7"/>
@@ -9043,7 +9048,7 @@
       </c>
       <c r="D238" s="7"/>
       <c t="s" r="E238" s="7">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="F238" s="7">
         <v>321</v>
@@ -9055,10 +9060,10 @@
         <v>47</v>
       </c>
       <c t="s" r="I238" s="7">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c t="s" r="J238" s="7">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="K238" s="7"/>
       <c r="L238" s="7"/>
@@ -9076,7 +9081,7 @@
       </c>
       <c r="D239" s="7"/>
       <c t="s" r="E239" s="7">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="F239" s="7">
         <v>321</v>
@@ -9088,10 +9093,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I239" s="7">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c t="s" r="J239" s="7">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="K239" s="7"/>
       <c r="L239" s="7"/>
@@ -9109,7 +9114,7 @@
       </c>
       <c r="D240" s="7"/>
       <c t="s" r="E240" s="7">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="F240" s="7">
         <v>321</v>
@@ -9121,7 +9126,7 @@
         <v>47</v>
       </c>
       <c t="s" r="I240" s="7">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c t="s" r="J240" s="7">
         <v>25</v>
@@ -9142,7 +9147,7 @@
       </c>
       <c r="D241" s="7"/>
       <c t="s" r="E241" s="7">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="F241" s="7">
         <v>321</v>
@@ -9154,10 +9159,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I241" s="7">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c t="s" r="J241" s="7">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="K241" s="7"/>
       <c r="L241" s="7"/>
@@ -9190,22 +9195,22 @@
       </c>
       <c r="D243" s="7"/>
       <c t="s" r="E243" s="7">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="F243" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G243" s="8">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c t="s" r="H243" s="8">
         <v>47</v>
       </c>
       <c t="s" r="I243" s="7">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c t="s" r="J243" s="7">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="K243" s="7"/>
       <c r="L243" s="7"/>
@@ -9223,7 +9228,7 @@
       </c>
       <c r="D244" s="7"/>
       <c t="s" r="E244" s="7">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="F244" s="7">
         <v>321</v>
@@ -9232,13 +9237,13 @@
         <v>47</v>
       </c>
       <c t="s" r="H244" s="8">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c t="s" r="I244" s="7">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c t="s" r="J244" s="7">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="K244" s="7"/>
       <c r="L244" s="7"/>
@@ -9256,19 +9261,19 @@
       </c>
       <c r="D245" s="7"/>
       <c t="s" r="E245" s="7">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="F245" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G245" s="8">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c t="s" r="H245" s="8">
         <v>47</v>
       </c>
       <c t="s" r="I245" s="7">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c t="s" r="J245" s="7">
         <v>45</v>
@@ -9289,7 +9294,7 @@
       </c>
       <c r="D246" s="7"/>
       <c t="s" r="E246" s="7">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="F246" s="7">
         <v>321</v>
@@ -9301,7 +9306,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I246" s="7">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c t="s" r="J246" s="7">
         <v>53</v>
@@ -9322,7 +9327,7 @@
       </c>
       <c r="D247" s="7"/>
       <c t="s" r="E247" s="7">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="F247" s="7">
         <v>321</v>
@@ -9331,13 +9336,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H247" s="8">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c t="s" r="I247" s="7">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c t="s" r="J247" s="7">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="K247" s="7"/>
       <c r="L247" s="7"/>
@@ -9355,22 +9360,22 @@
       </c>
       <c r="D248" s="7"/>
       <c t="s" r="E248" s="7">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="F248" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G248" s="8">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c t="s" r="H248" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I248" s="7">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c t="s" r="J248" s="7">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="K248" s="7"/>
       <c r="L248" s="7"/>
@@ -9403,22 +9408,22 @@
       </c>
       <c r="D250" s="7"/>
       <c t="s" r="E250" s="7">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="F250" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G250" s="8">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c t="s" r="H250" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I250" s="7">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c t="s" r="J250" s="7">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="K250" s="7"/>
       <c r="L250" s="7"/>
@@ -9436,7 +9441,7 @@
       </c>
       <c r="D251" s="7"/>
       <c t="s" r="E251" s="7">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="F251" s="7">
         <v>321</v>
@@ -9445,13 +9450,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H251" s="8">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c t="s" r="I251" s="7">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c t="s" r="J251" s="7">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="K251" s="7"/>
       <c r="L251" s="7"/>
@@ -9469,22 +9474,22 @@
       </c>
       <c r="D252" s="7"/>
       <c t="s" r="E252" s="7">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="F252" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G252" s="8">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c t="s" r="H252" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I252" s="7">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c t="s" r="J252" s="7">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="K252" s="7"/>
       <c r="L252" s="7"/>
@@ -9495,14 +9500,14 @@
         <v>13</v>
       </c>
       <c t="s" r="B253" s="7">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c t="s" r="C253" s="7">
         <v>14</v>
       </c>
       <c r="D253" s="7"/>
       <c t="s" r="E253" s="7">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="F253" s="7">
         <v>321</v>
@@ -9511,20 +9516,20 @@
         <v>16</v>
       </c>
       <c t="s" r="H253" s="8">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c t="s" r="I253" s="7">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c t="s" r="J253" s="7">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c t="s" r="K253" s="7">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="L253" s="7"/>
       <c t="s" r="M253" s="7">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="254" ht="14.25" customHeight="1">
@@ -9532,36 +9537,36 @@
         <v>13</v>
       </c>
       <c t="s" r="B254" s="7">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c t="s" r="C254" s="7">
         <v>14</v>
       </c>
       <c r="D254" s="7"/>
       <c t="s" r="E254" s="7">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="F254" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G254" s="8">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c t="s" r="H254" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I254" s="7">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c t="s" r="J254" s="7">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c t="s" r="K254" s="7">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="L254" s="7"/>
       <c t="s" r="M254" s="7">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
     <row r="255" ht="15" customHeight="1">
@@ -9591,22 +9596,22 @@
       </c>
       <c r="D256" s="7"/>
       <c t="s" r="E256" s="7">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="F256" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G256" s="8">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c t="s" r="H256" s="8">
         <v>47</v>
       </c>
       <c t="s" r="I256" s="7">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c t="s" r="J256" s="7">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="K256" s="7"/>
       <c r="L256" s="7"/>
@@ -9624,7 +9629,7 @@
       </c>
       <c r="D257" s="7"/>
       <c t="s" r="E257" s="7">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="F257" s="7">
         <v>321</v>
@@ -9633,13 +9638,13 @@
         <v>47</v>
       </c>
       <c t="s" r="H257" s="8">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c t="s" r="I257" s="7">
         <v>20</v>
       </c>
       <c t="s" r="J257" s="7">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="K257" s="7"/>
       <c r="L257" s="7"/>
@@ -9657,22 +9662,22 @@
       </c>
       <c r="D258" s="7"/>
       <c t="s" r="E258" s="7">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="F258" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G258" s="8">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c t="s" r="H258" s="8">
         <v>47</v>
       </c>
       <c t="s" r="I258" s="7">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c t="s" r="J258" s="7">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="K258" s="7"/>
       <c r="L258" s="7"/>
@@ -9705,7 +9710,7 @@
       </c>
       <c r="D260" s="7"/>
       <c t="s" r="E260" s="7">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="F260" s="7">
         <v>321</v>
@@ -9714,10 +9719,10 @@
         <v>65</v>
       </c>
       <c t="s" r="H260" s="8">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c t="s" r="I260" s="7">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c t="s" r="J260" s="7">
         <v>18</v>
@@ -9738,22 +9743,22 @@
       </c>
       <c r="D261" s="7"/>
       <c t="s" r="E261" s="7">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="F261" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G261" s="8">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c t="s" r="H261" s="8">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c t="s" r="I261" s="7">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c t="s" r="J261" s="7">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="K261" s="7"/>
       <c r="L261" s="7"/>
@@ -9771,22 +9776,22 @@
       </c>
       <c r="D262" s="7"/>
       <c t="s" r="E262" s="7">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="F262" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G262" s="8">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c t="s" r="H262" s="8">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c t="s" r="I262" s="7">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c t="s" r="J262" s="7">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="K262" s="7"/>
       <c r="L262" s="7"/>
@@ -9804,22 +9809,22 @@
       </c>
       <c r="D263" s="7"/>
       <c t="s" r="E263" s="7">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="F263" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G263" s="8">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c t="s" r="H263" s="8">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c t="s" r="I263" s="7">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c t="s" r="J263" s="7">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="K263" s="7"/>
       <c r="L263" s="7"/>
@@ -9852,7 +9857,7 @@
       </c>
       <c r="D265" s="7"/>
       <c t="s" r="E265" s="7">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="F265" s="7">
         <v>321</v>
@@ -9864,17 +9869,17 @@
         <v>41</v>
       </c>
       <c t="s" r="I265" s="7">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c t="s" r="J265" s="7">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c t="s" r="K265" s="7">
         <v>18</v>
       </c>
       <c r="L265" s="7"/>
       <c t="s" r="M265" s="7">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="266" ht="14.25" customHeight="1">
@@ -9889,7 +9894,7 @@
       </c>
       <c r="D266" s="7"/>
       <c t="s" r="E266" s="7">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="F266" s="7">
         <v>321</v>
@@ -9901,7 +9906,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I266" s="7">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c t="s" r="J266" s="7">
         <v>40</v>
@@ -9915,14 +9920,14 @@
         <v>13</v>
       </c>
       <c t="s" r="B267" s="7">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c t="s" r="C267" s="7">
         <v>14</v>
       </c>
       <c r="D267" s="7"/>
       <c t="s" r="E267" s="7">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="F267" s="7">
         <v>321</v>
@@ -9931,20 +9936,20 @@
         <v>16</v>
       </c>
       <c t="s" r="H267" s="8">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c t="s" r="I267" s="7">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c t="s" r="J267" s="7">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c t="s" r="K267" s="7">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="L267" s="7"/>
       <c t="s" r="M267" s="7">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="268" ht="14.25" customHeight="1">
@@ -9959,22 +9964,22 @@
       </c>
       <c r="D268" s="7"/>
       <c t="s" r="E268" s="7">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="F268" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G268" s="8">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c t="s" r="H268" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I268" s="7">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c t="s" r="J268" s="7">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="K268" s="7"/>
       <c r="L268" s="7"/>
@@ -10007,7 +10012,7 @@
       </c>
       <c r="D270" s="7"/>
       <c t="s" r="E270" s="7">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="F270" s="7">
         <v>321</v>
@@ -10019,10 +10024,10 @@
         <v>41</v>
       </c>
       <c t="s" r="I270" s="7">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c t="s" r="J270" s="7">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="K270" s="7"/>
       <c r="L270" s="7"/>
@@ -10040,7 +10045,7 @@
       </c>
       <c r="D271" s="7"/>
       <c t="s" r="E271" s="7">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="F271" s="7">
         <v>321</v>
@@ -10052,10 +10057,10 @@
         <v>47</v>
       </c>
       <c t="s" r="I271" s="7">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c t="s" r="J271" s="7">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="K271" s="7"/>
       <c r="L271" s="7"/>
@@ -10073,7 +10078,7 @@
       </c>
       <c r="D272" s="7"/>
       <c t="s" r="E272" s="7">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="F272" s="7">
         <v>321</v>
@@ -10085,10 +10090,10 @@
         <v>66</v>
       </c>
       <c t="s" r="I272" s="7">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c t="s" r="J272" s="7">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="K272" s="7"/>
       <c r="L272" s="7"/>
@@ -10106,7 +10111,7 @@
       </c>
       <c r="D273" s="7"/>
       <c t="s" r="E273" s="7">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="F273" s="7">
         <v>321</v>
@@ -10118,10 +10123,10 @@
         <v>47</v>
       </c>
       <c t="s" r="I273" s="7">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c t="s" r="J273" s="7">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="K273" s="7"/>
       <c r="L273" s="7"/>
@@ -10139,7 +10144,7 @@
       </c>
       <c r="D274" s="7"/>
       <c t="s" r="E274" s="7">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="F274" s="7">
         <v>321</v>
@@ -10148,13 +10153,13 @@
         <v>47</v>
       </c>
       <c t="s" r="H274" s="8">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c t="s" r="I274" s="7">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c t="s" r="J274" s="7">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="K274" s="7"/>
       <c r="L274" s="7"/>
@@ -10172,22 +10177,22 @@
       </c>
       <c r="D275" s="7"/>
       <c t="s" r="E275" s="7">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="F275" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G275" s="8">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c t="s" r="H275" s="8">
         <v>47</v>
       </c>
       <c t="s" r="I275" s="7">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c t="s" r="J275" s="7">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="K275" s="7"/>
       <c r="L275" s="7"/>
@@ -10220,22 +10225,22 @@
       </c>
       <c r="D277" s="7"/>
       <c t="s" r="E277" s="7">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="F277" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G277" s="8">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c t="s" r="H277" s="8">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c t="s" r="I277" s="7">
         <v>39</v>
       </c>
       <c t="s" r="J277" s="7">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="K277" s="7"/>
       <c r="L277" s="7"/>
@@ -10253,22 +10258,22 @@
       </c>
       <c r="D278" s="7"/>
       <c t="s" r="E278" s="7">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="F278" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G278" s="8">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c t="s" r="H278" s="8">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c t="s" r="I278" s="7">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c t="s" r="J278" s="7">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="K278" s="7"/>
       <c r="L278" s="7"/>
@@ -10286,19 +10291,19 @@
       </c>
       <c r="D279" s="7"/>
       <c t="s" r="E279" s="7">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="F279" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G279" s="8">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c t="s" r="H279" s="8">
         <v>47</v>
       </c>
       <c t="s" r="I279" s="7">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c t="s" r="J279" s="7">
         <v>48</v>
@@ -10319,7 +10324,7 @@
       </c>
       <c r="D280" s="7"/>
       <c t="s" r="E280" s="7">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="F280" s="7">
         <v>320</v>
@@ -10328,13 +10333,13 @@
         <v>47</v>
       </c>
       <c t="s" r="H280" s="8">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c t="s" r="I280" s="7">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c t="s" r="J280" s="7">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="K280" s="7"/>
       <c r="L280" s="7"/>
@@ -10352,22 +10357,22 @@
       </c>
       <c r="D281" s="7"/>
       <c t="s" r="E281" s="7">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="F281" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G281" s="8">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c t="s" r="H281" s="8">
         <v>47</v>
       </c>
       <c t="s" r="I281" s="7">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c t="s" r="J281" s="7">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="K281" s="7"/>
       <c r="L281" s="7"/>
@@ -10385,7 +10390,7 @@
       </c>
       <c r="D282" s="7"/>
       <c t="s" r="E282" s="7">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="F282" s="7">
         <v>320</v>
@@ -10394,10 +10399,10 @@
         <v>47</v>
       </c>
       <c t="s" r="H282" s="8">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c t="s" r="I282" s="7">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c t="s" r="J282" s="7">
         <v>39</v>
@@ -10433,22 +10438,22 @@
       </c>
       <c r="D284" s="7"/>
       <c t="s" r="E284" s="7">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="F284" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G284" s="8">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c t="s" r="H284" s="8">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c t="s" r="I284" s="7">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c t="s" r="J284" s="7">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="K284" s="7"/>
       <c r="L284" s="7"/>
@@ -10466,19 +10471,19 @@
       </c>
       <c r="D285" s="7"/>
       <c t="s" r="E285" s="7">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="F285" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G285" s="8">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c t="s" r="H285" s="8">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c t="s" r="I285" s="7">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c t="s" r="J285" s="7">
         <v>49</v>
@@ -10499,22 +10504,22 @@
       </c>
       <c r="D286" s="7"/>
       <c t="s" r="E286" s="7">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="F286" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G286" s="8">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c t="s" r="H286" s="8">
         <v>65</v>
       </c>
       <c t="s" r="I286" s="7">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c t="s" r="J286" s="7">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="K286" s="7"/>
       <c r="L286" s="7"/>
@@ -10547,7 +10552,7 @@
       </c>
       <c r="D288" s="7"/>
       <c t="s" r="E288" s="7">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="F288" s="7">
         <v>320</v>
@@ -10559,10 +10564,10 @@
         <v>66</v>
       </c>
       <c t="s" r="I288" s="7">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c t="s" r="J288" s="7">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="K288" s="7"/>
       <c r="L288" s="7"/>
@@ -10580,7 +10585,7 @@
       </c>
       <c r="D289" s="7"/>
       <c t="s" r="E289" s="7">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="F289" s="7">
         <v>320</v>
@@ -10592,10 +10597,10 @@
         <v>47</v>
       </c>
       <c t="s" r="I289" s="7">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c t="s" r="J289" s="7">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="K289" s="7"/>
       <c r="L289" s="7"/>
@@ -10613,7 +10618,7 @@
       </c>
       <c r="D290" s="7"/>
       <c t="s" r="E290" s="7">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="F290" s="7">
         <v>320</v>
@@ -10622,13 +10627,13 @@
         <v>47</v>
       </c>
       <c t="s" r="H290" s="8">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c t="s" r="I290" s="7">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c t="s" r="J290" s="7">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="K290" s="7"/>
       <c r="L290" s="7"/>
@@ -10646,22 +10651,22 @@
       </c>
       <c r="D291" s="7"/>
       <c t="s" r="E291" s="7">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="F291" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G291" s="8">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c t="s" r="H291" s="8">
         <v>47</v>
       </c>
       <c t="s" r="I291" s="7">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c t="s" r="J291" s="7">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="K291" s="7"/>
       <c r="L291" s="7"/>
@@ -10679,7 +10684,7 @@
       </c>
       <c r="D292" s="7"/>
       <c t="s" r="E292" s="7">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="F292" s="7">
         <v>320</v>
@@ -10688,13 +10693,13 @@
         <v>47</v>
       </c>
       <c t="s" r="H292" s="8">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c t="s" r="I292" s="7">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c t="s" r="J292" s="7">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="K292" s="7"/>
       <c r="L292" s="7"/>
@@ -10712,22 +10717,22 @@
       </c>
       <c r="D293" s="7"/>
       <c t="s" r="E293" s="7">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="F293" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G293" s="8">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c t="s" r="H293" s="8">
         <v>47</v>
       </c>
       <c t="s" r="I293" s="7">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c t="s" r="J293" s="7">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="K293" s="7"/>
       <c r="L293" s="7"/>
@@ -10745,7 +10750,7 @@
       </c>
       <c r="D294" s="7"/>
       <c t="s" r="E294" s="7">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="F294" s="7">
         <v>320</v>
@@ -10754,10 +10759,10 @@
         <v>47</v>
       </c>
       <c t="s" r="H294" s="8">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c t="s" r="I294" s="7">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c t="s" r="J294" s="7">
         <v>32</v>
@@ -10778,13 +10783,13 @@
       </c>
       <c r="D295" s="7"/>
       <c t="s" r="E295" s="7">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="F295" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G295" s="8">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c t="s" r="H295" s="8">
         <v>47</v>
@@ -10793,7 +10798,7 @@
         <v>35</v>
       </c>
       <c t="s" r="J295" s="7">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="K295" s="7"/>
       <c r="L295" s="7"/>
@@ -10826,7 +10831,7 @@
       </c>
       <c r="D297" s="7"/>
       <c t="s" r="E297" s="7">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="F297" s="7">
         <v>321</v>
@@ -10835,13 +10840,13 @@
         <v>47</v>
       </c>
       <c t="s" r="H297" s="8">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c t="s" r="I297" s="7">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c t="s" r="J297" s="7">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="K297" s="7"/>
       <c r="L297" s="7"/>
@@ -10859,19 +10864,19 @@
       </c>
       <c r="D298" s="7"/>
       <c t="s" r="E298" s="7">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="F298" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G298" s="8">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c t="s" r="H298" s="8">
         <v>47</v>
       </c>
       <c t="s" r="I298" s="7">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c t="s" r="J298" s="7">
         <v>40</v>
@@ -10892,7 +10897,7 @@
       </c>
       <c r="D299" s="7"/>
       <c t="s" r="E299" s="7">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="F299" s="7">
         <v>321</v>
@@ -10901,13 +10906,13 @@
         <v>47</v>
       </c>
       <c t="s" r="H299" s="8">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c t="s" r="I299" s="7">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c t="s" r="J299" s="7">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="K299" s="7"/>
       <c r="L299" s="7"/>
@@ -10925,13 +10930,13 @@
       </c>
       <c r="D300" s="7"/>
       <c t="s" r="E300" s="7">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="F300" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G300" s="8">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c t="s" r="H300" s="8">
         <v>47</v>
@@ -10958,7 +10963,7 @@
       </c>
       <c r="D301" s="7"/>
       <c t="s" r="E301" s="7">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="F301" s="7">
         <v>321</v>
@@ -10967,13 +10972,13 @@
         <v>47</v>
       </c>
       <c t="s" r="H301" s="8">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c t="s" r="I301" s="7">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c t="s" r="J301" s="7">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="K301" s="7"/>
       <c r="L301" s="7"/>
@@ -11006,22 +11011,22 @@
       </c>
       <c r="D303" s="7"/>
       <c t="s" r="E303" s="7">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="F303" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G303" s="8">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c t="s" r="H303" s="8">
         <v>47</v>
       </c>
       <c t="s" r="I303" s="7">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c t="s" r="J303" s="7">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="K303" s="7"/>
       <c r="L303" s="7"/>
@@ -11039,7 +11044,7 @@
       </c>
       <c r="D304" s="7"/>
       <c t="s" r="E304" s="7">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="F304" s="7">
         <v>320</v>
@@ -11048,10 +11053,10 @@
         <v>47</v>
       </c>
       <c t="s" r="H304" s="8">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c t="s" r="I304" s="7">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c t="s" r="J304" s="7">
         <v>19</v>
@@ -11072,13 +11077,13 @@
       </c>
       <c r="D305" s="7"/>
       <c t="s" r="E305" s="7">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="F305" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G305" s="8">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c t="s" r="H305" s="8">
         <v>47</v>
@@ -11087,7 +11092,7 @@
         <v>40</v>
       </c>
       <c t="s" r="J305" s="7">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="K305" s="7"/>
       <c r="L305" s="7"/>
@@ -11105,7 +11110,7 @@
       </c>
       <c r="D306" s="7"/>
       <c t="s" r="E306" s="7">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="F306" s="7">
         <v>320</v>
@@ -11114,13 +11119,13 @@
         <v>47</v>
       </c>
       <c t="s" r="H306" s="8">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c t="s" r="I306" s="7">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c t="s" r="J306" s="7">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="K306" s="7"/>
       <c r="L306" s="7"/>
@@ -11138,22 +11143,22 @@
       </c>
       <c r="D307" s="7"/>
       <c t="s" r="E307" s="7">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="F307" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G307" s="8">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c t="s" r="H307" s="8">
         <v>47</v>
       </c>
       <c t="s" r="I307" s="7">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c t="s" r="J307" s="7">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="K307" s="7"/>
       <c r="L307" s="7"/>
@@ -11171,7 +11176,7 @@
       </c>
       <c r="D308" s="7"/>
       <c t="s" r="E308" s="7">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="F308" s="7">
         <v>320</v>
@@ -11180,13 +11185,13 @@
         <v>47</v>
       </c>
       <c t="s" r="H308" s="8">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c t="s" r="I308" s="7">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c t="s" r="J308" s="7">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="K308" s="7"/>
       <c r="L308" s="7"/>
@@ -11204,22 +11209,22 @@
       </c>
       <c r="D309" s="7"/>
       <c t="s" r="E309" s="7">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="F309" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G309" s="8">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c t="s" r="H309" s="8">
         <v>47</v>
       </c>
       <c t="s" r="I309" s="7">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c t="s" r="J309" s="7">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="K309" s="7"/>
       <c r="L309" s="7"/>
@@ -11252,7 +11257,7 @@
       </c>
       <c r="D311" s="7"/>
       <c t="s" r="E311" s="7">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="F311" s="7">
         <v>320</v>
@@ -11261,13 +11266,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H311" s="8">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c t="s" r="I311" s="7">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c t="s" r="J311" s="7">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="K311" s="7"/>
       <c r="L311" s="7"/>
@@ -11285,22 +11290,22 @@
       </c>
       <c r="D312" s="7"/>
       <c t="s" r="E312" s="7">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="F312" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G312" s="8">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c t="s" r="H312" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I312" s="7">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c t="s" r="J312" s="7">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="K312" s="7"/>
       <c r="L312" s="7"/>
@@ -11311,14 +11316,14 @@
         <v>13</v>
       </c>
       <c t="s" r="B313" s="7">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c t="s" r="C313" s="7">
         <v>14</v>
       </c>
       <c r="D313" s="7"/>
       <c t="s" r="E313" s="7">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="F313" s="7">
         <v>320</v>
@@ -11333,14 +11338,14 @@
         <v>39</v>
       </c>
       <c t="s" r="J313" s="7">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c t="s" r="K313" s="7">
         <v>39</v>
       </c>
       <c r="L313" s="7"/>
       <c t="s" r="M313" s="7">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="314" ht="14.25" customHeight="1">
@@ -11355,7 +11360,7 @@
       </c>
       <c r="D314" s="7"/>
       <c t="s" r="E314" s="7">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="F314" s="7">
         <v>320</v>
@@ -11364,13 +11369,13 @@
         <v>47</v>
       </c>
       <c t="s" r="H314" s="8">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c t="s" r="I314" s="7">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c t="s" r="J314" s="7">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="K314" s="7"/>
       <c r="L314" s="7"/>
@@ -11388,22 +11393,22 @@
       </c>
       <c r="D315" s="7"/>
       <c t="s" r="E315" s="7">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="F315" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G315" s="8">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c t="s" r="H315" s="8">
         <v>47</v>
       </c>
       <c t="s" r="I315" s="7">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c t="s" r="J315" s="7">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="K315" s="7"/>
       <c r="L315" s="7"/>
@@ -11414,14 +11419,14 @@
         <v>13</v>
       </c>
       <c t="s" r="B316" s="7">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c t="s" r="C316" s="7">
         <v>14</v>
       </c>
       <c r="D316" s="7"/>
       <c t="s" r="E316" s="7">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="F316" s="7">
         <v>320</v>
@@ -11430,16 +11435,16 @@
         <v>47</v>
       </c>
       <c t="s" r="H316" s="8">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c t="s" r="I316" s="7">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c t="s" r="J316" s="7">
         <v>53</v>
       </c>
       <c t="s" r="K316" s="7">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="L316" s="7"/>
       <c t="s" r="M316" s="7">
@@ -11451,36 +11456,36 @@
         <v>13</v>
       </c>
       <c t="s" r="B317" s="7">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c t="s" r="C317" s="7">
         <v>14</v>
       </c>
       <c r="D317" s="7"/>
       <c t="s" r="E317" s="7">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="F317" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G317" s="8">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c t="s" r="H317" s="8">
         <v>47</v>
       </c>
       <c t="s" r="I317" s="7">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c t="s" r="J317" s="7">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c t="s" r="K317" s="7">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="L317" s="7"/>
       <c t="s" r="M317" s="7">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="318" ht="14.25" customHeight="1">
@@ -11510,22 +11515,22 @@
       </c>
       <c r="D319" s="7"/>
       <c t="s" r="E319" s="7">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="F319" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G319" s="8">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c t="s" r="H319" s="8">
         <v>66</v>
       </c>
       <c t="s" r="I319" s="7">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c t="s" r="J319" s="7">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="K319" s="7"/>
       <c r="L319" s="7"/>
@@ -11543,7 +11548,7 @@
       </c>
       <c r="D320" s="7"/>
       <c t="s" r="E320" s="7">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="F320" s="7">
         <v>321</v>
@@ -11552,13 +11557,13 @@
         <v>66</v>
       </c>
       <c t="s" r="H320" s="8">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c t="s" r="I320" s="7">
         <v>18</v>
       </c>
       <c t="s" r="J320" s="7">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="K320" s="7"/>
       <c r="L320" s="7"/>
@@ -11576,22 +11581,22 @@
       </c>
       <c r="D321" s="7"/>
       <c t="s" r="E321" s="7">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="F321" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G321" s="8">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c t="s" r="H321" s="8">
+        <v>125</v>
+      </c>
+      <c t="s" r="I321" s="7">
         <v>124</v>
       </c>
-      <c t="s" r="I321" s="7">
-        <v>123</v>
-      </c>
       <c t="s" r="J321" s="7">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="K321" s="7"/>
       <c r="L321" s="7"/>
@@ -11609,22 +11614,22 @@
       </c>
       <c r="D322" s="7"/>
       <c t="s" r="E322" s="7">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="F322" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G322" s="8">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c t="s" r="H322" s="8">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c t="s" r="I322" s="7">
         <v>21</v>
       </c>
       <c t="s" r="J322" s="7">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="K322" s="7"/>
       <c r="L322" s="7"/>
@@ -11638,26 +11643,26 @@
         <v>5840</v>
       </c>
       <c t="s" r="C323" s="7">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="D323" s="7"/>
       <c t="s" r="E323" s="7">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="F323" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G323" s="8">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c t="s" r="H323" s="8">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c t="s" r="I323" s="7">
         <v>53</v>
       </c>
       <c t="s" r="J323" s="7">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="K323" s="7"/>
       <c r="L323" s="7"/>
@@ -11671,26 +11676,26 @@
         <v>5841</v>
       </c>
       <c t="s" r="C324" s="7">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="D324" s="7"/>
       <c t="s" r="E324" s="7">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="F324" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G324" s="8">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c t="s" r="H324" s="8">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c t="s" r="I324" s="7">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c t="s" r="J324" s="7">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="K324" s="7"/>
       <c r="L324" s="7"/>
@@ -11723,7 +11728,7 @@
       </c>
       <c r="D326" s="7"/>
       <c t="s" r="E326" s="7">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="F326" s="7">
         <v>320</v>
@@ -11735,10 +11740,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I326" s="7">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c t="s" r="J326" s="7">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="K326" s="7"/>
       <c r="L326" s="7"/>
@@ -11756,7 +11761,7 @@
       </c>
       <c r="D327" s="7"/>
       <c t="s" r="E327" s="7">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="F327" s="7">
         <v>320</v>
@@ -11768,10 +11773,10 @@
         <v>66</v>
       </c>
       <c t="s" r="I327" s="7">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c t="s" r="J327" s="7">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="K327" s="7"/>
       <c r="L327" s="7"/>
@@ -11789,7 +11794,7 @@
       </c>
       <c r="D328" s="7"/>
       <c t="s" r="E328" s="7">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="F328" s="7">
         <v>320</v>
@@ -11801,10 +11806,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I328" s="7">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c t="s" r="J328" s="7">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="K328" s="7"/>
       <c r="L328" s="7"/>
@@ -11822,7 +11827,7 @@
       </c>
       <c r="D329" s="7"/>
       <c t="s" r="E329" s="7">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="F329" s="7">
         <v>320</v>
@@ -11834,10 +11839,10 @@
         <v>47</v>
       </c>
       <c t="s" r="I329" s="7">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c t="s" r="J329" s="7">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="K329" s="7"/>
       <c r="L329" s="7"/>
@@ -11855,7 +11860,7 @@
       </c>
       <c r="D330" s="7"/>
       <c t="s" r="E330" s="7">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="F330" s="7">
         <v>320</v>
@@ -11867,7 +11872,7 @@
         <v>23</v>
       </c>
       <c t="s" r="I330" s="7">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c t="s" r="J330" s="7">
         <v>21</v>
@@ -11888,7 +11893,7 @@
       </c>
       <c r="D331" s="7"/>
       <c t="s" r="E331" s="7">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="F331" s="7">
         <v>320</v>
@@ -11900,10 +11905,10 @@
         <v>47</v>
       </c>
       <c t="s" r="I331" s="7">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c t="s" r="J331" s="7">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="K331" s="7"/>
       <c r="L331" s="7"/>
@@ -11914,14 +11919,14 @@
         <v>13</v>
       </c>
       <c t="s" r="B332" s="7">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c t="s" r="C332" s="7">
         <v>14</v>
       </c>
       <c r="D332" s="7"/>
       <c t="s" r="E332" s="7">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="F332" s="7">
         <v>320</v>
@@ -11930,20 +11935,20 @@
         <v>47</v>
       </c>
       <c t="s" r="H332" s="8">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c t="s" r="I332" s="7">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c t="s" r="J332" s="7">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c t="s" r="K332" s="7">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="L332" s="7"/>
       <c t="s" r="M332" s="7">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="333" ht="14.25" customHeight="1">
@@ -11951,20 +11956,20 @@
         <v>13</v>
       </c>
       <c t="s" r="B333" s="7">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c t="s" r="C333" s="7">
         <v>14</v>
       </c>
       <c r="D333" s="7"/>
       <c t="s" r="E333" s="7">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="F333" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G333" s="8">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c t="s" r="H333" s="8">
         <v>47</v>
@@ -11973,14 +11978,14 @@
         <v>53</v>
       </c>
       <c t="s" r="J333" s="7">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c t="s" r="K333" s="7">
         <v>53</v>
       </c>
       <c r="L333" s="7"/>
       <c t="s" r="M333" s="7">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="334" ht="14.25" customHeight="1">
@@ -12010,22 +12015,22 @@
       </c>
       <c r="D335" s="7"/>
       <c t="s" r="E335" s="7">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="F335" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G335" s="8">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c t="s" r="H335" s="8">
         <v>66</v>
       </c>
       <c t="s" r="I335" s="7">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c t="s" r="J335" s="7">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="K335" s="7"/>
       <c r="L335" s="7"/>
@@ -12043,7 +12048,7 @@
       </c>
       <c r="D336" s="7"/>
       <c t="s" r="E336" s="7">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="F336" s="7">
         <v>321</v>
@@ -12052,13 +12057,13 @@
         <v>66</v>
       </c>
       <c t="s" r="H336" s="8">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c t="s" r="I336" s="7">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c t="s" r="J336" s="7">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="K336" s="7"/>
       <c r="L336" s="7"/>
@@ -12076,13 +12081,13 @@
       </c>
       <c r="D337" s="7"/>
       <c t="s" r="E337" s="7">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="F337" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G337" s="8">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c t="s" r="H337" s="8">
         <v>66</v>
@@ -12091,7 +12096,7 @@
         <v>21</v>
       </c>
       <c t="s" r="J337" s="7">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="K337" s="7"/>
       <c r="L337" s="7"/>
@@ -12109,7 +12114,7 @@
       </c>
       <c r="D338" s="7"/>
       <c t="s" r="E338" s="7">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="F338" s="7">
         <v>321</v>
@@ -12121,10 +12126,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I338" s="7">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c t="s" r="J338" s="7">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="K338" s="7"/>
       <c r="L338" s="7"/>
@@ -12142,7 +12147,7 @@
       </c>
       <c r="D339" s="7"/>
       <c t="s" r="E339" s="7">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="F339" s="7">
         <v>321</v>
@@ -12151,13 +12156,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H339" s="8">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c t="s" r="I339" s="7">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c t="s" r="J339" s="7">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="K339" s="7"/>
       <c r="L339" s="7"/>
@@ -12175,19 +12180,19 @@
       </c>
       <c r="D340" s="7"/>
       <c t="s" r="E340" s="7">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="F340" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G340" s="8">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c t="s" r="H340" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I340" s="7">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c t="s" r="J340" s="7">
         <v>32</v>
@@ -12208,7 +12213,7 @@
       </c>
       <c r="D341" s="7"/>
       <c t="s" r="E341" s="7">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="F341" s="7">
         <v>321</v>
@@ -12220,10 +12225,10 @@
         <v>65</v>
       </c>
       <c t="s" r="I341" s="7">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c t="s" r="J341" s="7">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="K341" s="7"/>
       <c r="L341" s="7"/>
@@ -12249,14 +12254,14 @@
         <v>13</v>
       </c>
       <c t="s" r="B343" s="7">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c t="s" r="C343" s="7">
         <v>14</v>
       </c>
       <c r="D343" s="7"/>
       <c t="s" r="E343" s="7">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="F343" s="7">
         <v>320</v>
@@ -12265,20 +12270,20 @@
         <v>16</v>
       </c>
       <c t="s" r="H343" s="8">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c t="s" r="I343" s="7">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c t="s" r="J343" s="7">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c t="s" r="K343" s="7">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="L343" s="7"/>
       <c t="s" r="M343" s="7">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="344" ht="14.25" customHeight="1">
@@ -12286,32 +12291,32 @@
         <v>13</v>
       </c>
       <c t="s" r="B344" s="7">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c t="s" r="C344" s="7">
         <v>14</v>
       </c>
       <c r="D344" s="7"/>
       <c t="s" r="E344" s="7">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="F344" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G344" s="8">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c t="s" r="H344" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I344" s="7">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c t="s" r="J344" s="7">
         <v>18</v>
       </c>
       <c t="s" r="K344" s="7">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="L344" s="7"/>
       <c t="s" r="M344" s="7">
@@ -12323,14 +12328,14 @@
         <v>13</v>
       </c>
       <c t="s" r="B345" s="7">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c t="s" r="C345" s="7">
         <v>14</v>
       </c>
       <c r="D345" s="7"/>
       <c t="s" r="E345" s="7">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="F345" s="7">
         <v>320</v>
@@ -12339,20 +12344,20 @@
         <v>16</v>
       </c>
       <c t="s" r="H345" s="8">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c t="s" r="I345" s="7">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c t="s" r="J345" s="7">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c t="s" r="K345" s="7">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="L345" s="7"/>
       <c t="s" r="M345" s="7">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="346" ht="14.25" customHeight="1">
@@ -12360,32 +12365,32 @@
         <v>13</v>
       </c>
       <c t="s" r="B346" s="7">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c t="s" r="C346" s="7">
         <v>14</v>
       </c>
       <c r="D346" s="7"/>
       <c t="s" r="E346" s="7">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="F346" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G346" s="8">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c t="s" r="H346" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I346" s="7">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c t="s" r="J346" s="7">
         <v>40</v>
       </c>
       <c t="s" r="K346" s="7">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="L346" s="7"/>
       <c t="s" r="M346" s="7">
@@ -12397,14 +12402,14 @@
         <v>13</v>
       </c>
       <c t="s" r="B347" s="7">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c t="s" r="C347" s="7">
         <v>14</v>
       </c>
       <c r="D347" s="7"/>
       <c t="s" r="E347" s="7">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="F347" s="7">
         <v>320</v>
@@ -12413,20 +12418,20 @@
         <v>16</v>
       </c>
       <c t="s" r="H347" s="8">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c t="s" r="I347" s="7">
         <v>20</v>
       </c>
       <c t="s" r="J347" s="7">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c t="s" r="K347" s="7">
         <v>20</v>
       </c>
       <c r="L347" s="7"/>
       <c t="s" r="M347" s="7">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="348" ht="14.25" customHeight="1">
@@ -12434,32 +12439,32 @@
         <v>13</v>
       </c>
       <c t="s" r="B348" s="7">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c t="s" r="C348" s="7">
         <v>14</v>
       </c>
       <c r="D348" s="7"/>
       <c t="s" r="E348" s="7">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="F348" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G348" s="8">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c t="s" r="H348" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I348" s="7">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c t="s" r="J348" s="7">
         <v>59</v>
       </c>
       <c t="s" r="K348" s="7">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L348" s="7"/>
       <c t="s" r="M348" s="7">
@@ -12478,7 +12483,7 @@
       </c>
       <c r="D349" s="7"/>
       <c t="s" r="E349" s="7">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="F349" s="7">
         <v>320</v>
@@ -12487,13 +12492,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H349" s="8">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c t="s" r="I349" s="7">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c t="s" r="J349" s="7">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="K349" s="7"/>
       <c r="L349" s="7"/>
@@ -12511,19 +12516,19 @@
       </c>
       <c r="D350" s="7"/>
       <c t="s" r="E350" s="7">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="F350" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G350" s="8">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c t="s" r="H350" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I350" s="7">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c t="s" r="J350" s="7">
         <v>60</v>
@@ -12544,7 +12549,7 @@
       </c>
       <c r="D351" s="7"/>
       <c t="s" r="E351" s="7">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="F351" s="7">
         <v>320</v>
@@ -12556,10 +12561,10 @@
         <v>47</v>
       </c>
       <c t="s" r="I351" s="7">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c t="s" r="J351" s="7">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="K351" s="7"/>
       <c r="L351" s="7"/>
@@ -12592,7 +12597,7 @@
       </c>
       <c r="D353" s="7"/>
       <c t="s" r="E353" s="7">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="F353" s="7">
         <v>320</v>
@@ -12604,10 +12609,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I353" s="7">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c t="s" r="J353" s="7">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="K353" s="7"/>
       <c r="L353" s="7"/>
@@ -12625,7 +12630,7 @@
       </c>
       <c r="D354" s="7"/>
       <c t="s" r="E354" s="7">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="F354" s="7">
         <v>320</v>
@@ -12637,10 +12642,10 @@
         <v>47</v>
       </c>
       <c t="s" r="I354" s="7">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c t="s" r="J354" s="7">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="K354" s="7"/>
       <c r="L354" s="7"/>
@@ -12658,7 +12663,7 @@
       </c>
       <c r="D355" s="7"/>
       <c t="s" r="E355" s="7">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="F355" s="7">
         <v>320</v>
@@ -12670,10 +12675,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I355" s="7">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c t="s" r="J355" s="7">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="K355" s="7"/>
       <c r="L355" s="7"/>
@@ -12684,14 +12689,14 @@
         <v>13</v>
       </c>
       <c t="s" r="B356" s="7">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c t="s" r="C356" s="7">
         <v>14</v>
       </c>
       <c r="D356" s="7"/>
       <c t="s" r="E356" s="7">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="F356" s="7">
         <v>320</v>
@@ -12703,17 +12708,17 @@
         <v>66</v>
       </c>
       <c t="s" r="I356" s="7">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c t="s" r="J356" s="7">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c t="s" r="K356" s="7">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="L356" s="7"/>
       <c t="s" r="M356" s="7">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="357" ht="14.25" customHeight="1">
@@ -12721,14 +12726,14 @@
         <v>13</v>
       </c>
       <c t="s" r="B357" s="7">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c t="s" r="C357" s="7">
         <v>14</v>
       </c>
       <c r="D357" s="7"/>
       <c t="s" r="E357" s="7">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="F357" s="7">
         <v>320</v>
@@ -12740,13 +12745,13 @@
         <v>16</v>
       </c>
       <c t="s" r="I357" s="7">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c t="s" r="J357" s="7">
         <v>24</v>
       </c>
       <c t="s" r="K357" s="7">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="L357" s="7"/>
       <c t="s" r="M357" s="7">
@@ -12765,7 +12770,7 @@
       </c>
       <c r="D358" s="7"/>
       <c t="s" r="E358" s="7">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="F358" s="7">
         <v>320</v>
@@ -12774,13 +12779,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H358" s="8">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c t="s" r="I358" s="7">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c t="s" r="J358" s="7">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="K358" s="7"/>
       <c r="L358" s="7"/>
@@ -12798,22 +12803,22 @@
       </c>
       <c r="D359" s="7"/>
       <c t="s" r="E359" s="7">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="F359" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G359" s="8">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c t="s" r="H359" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I359" s="7">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c t="s" r="J359" s="7">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="K359" s="7"/>
       <c r="L359" s="7"/>
@@ -12838,15 +12843,15 @@
       <c t="s" r="A361" s="6">
         <v>13</v>
       </c>
-      <c r="B361" s="7">
-        <v>849</v>
+      <c t="s" r="B361" s="7">
+        <v>401</v>
       </c>
       <c t="s" r="C361" s="7">
         <v>14</v>
       </c>
       <c r="D361" s="7"/>
       <c t="s" r="E361" s="7">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="F361" s="7">
         <v>321</v>
@@ -12855,46 +12860,50 @@
         <v>16</v>
       </c>
       <c t="s" r="H361" s="8">
-        <v>57</v>
+        <v>279</v>
       </c>
       <c t="s" r="I361" s="7">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c t="s" r="J361" s="7">
-        <v>257</v>
-      </c>
-      <c r="K361" s="7"/>
+        <v>286</v>
+      </c>
+      <c t="s" r="K361" s="7">
+        <v>126</v>
+      </c>
       <c r="L361" s="7"/>
-      <c r="M361" s="7"/>
+      <c t="s" r="M361" s="7">
+        <v>286</v>
+      </c>
     </row>
     <row r="362" ht="14.25" customHeight="1">
       <c t="s" r="A362" s="6">
         <v>13</v>
       </c>
       <c r="B362" s="7">
-        <v>848</v>
+        <v>970</v>
       </c>
       <c t="s" r="C362" s="7">
         <v>14</v>
       </c>
       <c r="D362" s="7"/>
       <c t="s" r="E362" s="7">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="F362" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G362" s="8">
-        <v>57</v>
+        <v>279</v>
       </c>
       <c t="s" r="H362" s="8">
-        <v>16</v>
+        <v>141</v>
       </c>
       <c t="s" r="I362" s="7">
-        <v>110</v>
+        <v>355</v>
       </c>
       <c t="s" r="J362" s="7">
-        <v>72</v>
+        <v>222</v>
       </c>
       <c r="K362" s="7"/>
       <c r="L362" s="7"/>
@@ -12905,29 +12914,29 @@
         <v>13</v>
       </c>
       <c r="B363" s="7">
-        <v>282</v>
+        <v>2856</v>
       </c>
       <c t="s" r="C363" s="7">
-        <v>14</v>
+        <v>241</v>
       </c>
       <c r="D363" s="7"/>
       <c t="s" r="E363" s="7">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="F363" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G363" s="8">
-        <v>16</v>
+        <v>141</v>
       </c>
       <c t="s" r="H363" s="8">
-        <v>78</v>
+        <v>403</v>
       </c>
       <c t="s" r="I363" s="7">
-        <v>168</v>
+        <v>111</v>
       </c>
       <c t="s" r="J363" s="7">
-        <v>401</v>
+        <v>142</v>
       </c>
       <c r="K363" s="7"/>
       <c r="L363" s="7"/>
@@ -12938,114 +12947,110 @@
         <v>13</v>
       </c>
       <c r="B364" s="7">
-        <v>926</v>
+        <v>2857</v>
       </c>
       <c t="s" r="C364" s="7">
-        <v>14</v>
+        <v>241</v>
       </c>
       <c r="D364" s="7"/>
       <c t="s" r="E364" s="7">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="F364" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G364" s="8">
-        <v>78</v>
+        <v>403</v>
       </c>
       <c t="s" r="H364" s="8">
-        <v>65</v>
+        <v>141</v>
       </c>
       <c t="s" r="I364" s="7">
-        <v>118</v>
+        <v>159</v>
       </c>
       <c t="s" r="J364" s="7">
-        <v>402</v>
+        <v>260</v>
       </c>
       <c r="K364" s="7"/>
       <c r="L364" s="7"/>
       <c r="M364" s="7"/>
     </row>
     <row r="365" ht="15" customHeight="1">
-      <c r="A365" s="6"/>
-      <c r="B365" s="7"/>
-      <c r="C365" s="7"/>
+      <c t="s" r="A365" s="6">
+        <v>13</v>
+      </c>
+      <c r="B365" s="7">
+        <v>878</v>
+      </c>
+      <c t="s" r="C365" s="7">
+        <v>14</v>
+      </c>
       <c r="D365" s="7"/>
-      <c r="E365" s="7"/>
-      <c r="F365" s="7"/>
-      <c r="G365" s="8"/>
-      <c r="H365" s="8"/>
-      <c r="I365" s="7"/>
-      <c r="J365" s="7"/>
+      <c t="s" r="E365" s="7">
+        <v>402</v>
+      </c>
+      <c r="F365" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G365" s="8">
+        <v>141</v>
+      </c>
+      <c t="s" r="H365" s="8">
+        <v>65</v>
+      </c>
+      <c t="s" r="I365" s="7">
+        <v>404</v>
+      </c>
+      <c t="s" r="J365" s="7">
+        <v>377</v>
+      </c>
       <c r="K365" s="7"/>
       <c r="L365" s="7"/>
       <c r="M365" s="7"/>
     </row>
     <row r="366" ht="14.25" customHeight="1">
-      <c t="s" r="A366" s="6">
-        <v>13</v>
-      </c>
-      <c t="s" r="B366" s="7">
-        <v>403</v>
-      </c>
-      <c t="s" r="C366" s="7">
-        <v>14</v>
-      </c>
+      <c r="A366" s="6"/>
+      <c r="B366" s="7"/>
+      <c r="C366" s="7"/>
       <c r="D366" s="7"/>
-      <c t="s" r="E366" s="7">
-        <v>404</v>
-      </c>
-      <c r="F366" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G366" s="8">
-        <v>16</v>
-      </c>
-      <c t="s" r="H366" s="8">
-        <v>278</v>
-      </c>
-      <c t="s" r="I366" s="7">
-        <v>125</v>
-      </c>
-      <c t="s" r="J366" s="7">
-        <v>285</v>
-      </c>
-      <c t="s" r="K366" s="7">
-        <v>125</v>
-      </c>
+      <c r="E366" s="7"/>
+      <c r="F366" s="7"/>
+      <c r="G366" s="8"/>
+      <c r="H366" s="8"/>
+      <c r="I366" s="7"/>
+      <c r="J366" s="7"/>
+      <c r="K366" s="7"/>
       <c r="L366" s="7"/>
-      <c t="s" r="M366" s="7">
-        <v>285</v>
-      </c>
+      <c r="M366" s="7"/>
     </row>
     <row r="367" ht="14.25" customHeight="1">
       <c t="s" r="A367" s="6">
         <v>13</v>
       </c>
       <c r="B367" s="7">
-        <v>970</v>
+        <v>849</v>
       </c>
       <c t="s" r="C367" s="7">
         <v>14</v>
       </c>
       <c r="D367" s="7"/>
       <c t="s" r="E367" s="7">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="F367" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G367" s="8">
-        <v>278</v>
+        <v>16</v>
       </c>
       <c t="s" r="H367" s="8">
-        <v>140</v>
+        <v>57</v>
       </c>
       <c t="s" r="I367" s="7">
-        <v>354</v>
+        <v>121</v>
       </c>
       <c t="s" r="J367" s="7">
-        <v>221</v>
+        <v>258</v>
       </c>
       <c r="K367" s="7"/>
       <c r="L367" s="7"/>
@@ -13056,29 +13061,29 @@
         <v>13</v>
       </c>
       <c r="B368" s="7">
-        <v>2856</v>
+        <v>848</v>
       </c>
       <c t="s" r="C368" s="7">
-        <v>240</v>
+        <v>14</v>
       </c>
       <c r="D368" s="7"/>
       <c t="s" r="E368" s="7">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="F368" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G368" s="8">
-        <v>140</v>
+        <v>57</v>
       </c>
       <c t="s" r="H368" s="8">
-        <v>405</v>
+        <v>16</v>
       </c>
       <c t="s" r="I368" s="7">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c t="s" r="J368" s="7">
-        <v>141</v>
+        <v>73</v>
       </c>
       <c r="K368" s="7"/>
       <c r="L368" s="7"/>
@@ -13089,29 +13094,29 @@
         <v>13</v>
       </c>
       <c r="B369" s="7">
-        <v>2857</v>
+        <v>282</v>
       </c>
       <c t="s" r="C369" s="7">
-        <v>240</v>
+        <v>14</v>
       </c>
       <c r="D369" s="7"/>
       <c t="s" r="E369" s="7">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="F369" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G369" s="8">
-        <v>405</v>
+        <v>16</v>
       </c>
       <c t="s" r="H369" s="8">
-        <v>140</v>
+        <v>79</v>
       </c>
       <c t="s" r="I369" s="7">
-        <v>158</v>
+        <v>169</v>
       </c>
       <c t="s" r="J369" s="7">
-        <v>259</v>
+        <v>406</v>
       </c>
       <c r="K369" s="7"/>
       <c r="L369" s="7"/>
@@ -13122,29 +13127,29 @@
         <v>13</v>
       </c>
       <c r="B370" s="7">
-        <v>878</v>
+        <v>926</v>
       </c>
       <c t="s" r="C370" s="7">
         <v>14</v>
       </c>
       <c r="D370" s="7"/>
       <c t="s" r="E370" s="7">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="F370" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G370" s="8">
-        <v>140</v>
+        <v>79</v>
       </c>
       <c t="s" r="H370" s="8">
         <v>65</v>
       </c>
       <c t="s" r="I370" s="7">
-        <v>406</v>
+        <v>119</v>
       </c>
       <c t="s" r="J370" s="7">
-        <v>376</v>
+        <v>407</v>
       </c>
       <c r="K370" s="7"/>
       <c r="L370" s="7"/>
@@ -13177,7 +13182,7 @@
       </c>
       <c r="D372" s="7"/>
       <c t="s" r="E372" s="7">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="F372" s="7">
         <v>321</v>
@@ -13186,20 +13191,20 @@
         <v>65</v>
       </c>
       <c t="s" r="H372" s="8">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c t="s" r="I372" s="7">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c t="s" r="J372" s="7">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c t="s" r="K372" s="7">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="L372" s="7"/>
       <c t="s" r="M372" s="7">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="373" ht="14.25" customHeight="1">
@@ -13214,22 +13219,22 @@
       </c>
       <c r="D373" s="7"/>
       <c t="s" r="E373" s="7">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="F373" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G373" s="8">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c t="s" r="H373" s="8">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c t="s" r="I373" s="7">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c t="s" r="J373" s="7">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="K373" s="7"/>
       <c r="L373" s="7"/>
@@ -13247,22 +13252,22 @@
       </c>
       <c r="D374" s="7"/>
       <c t="s" r="E374" s="7">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="F374" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G374" s="8">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c t="s" r="H374" s="8">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c t="s" r="I374" s="7">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c t="s" r="J374" s="7">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="K374" s="7"/>
       <c r="L374" s="7"/>
@@ -13280,22 +13285,22 @@
       </c>
       <c r="D375" s="7"/>
       <c t="s" r="E375" s="7">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="F375" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G375" s="8">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c t="s" r="H375" s="8">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c t="s" r="I375" s="7">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c t="s" r="J375" s="7">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="K375" s="7"/>
       <c r="L375" s="7"/>
@@ -13313,22 +13318,22 @@
       </c>
       <c r="D376" s="7"/>
       <c t="s" r="E376" s="7">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="F376" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G376" s="8">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c t="s" r="H376" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I376" s="7">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c t="s" r="J376" s="7">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="K376" s="7"/>
       <c r="L376" s="7"/>
@@ -13346,7 +13351,7 @@
       </c>
       <c r="D377" s="7"/>
       <c t="s" r="E377" s="7">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="F377" s="7">
         <v>321</v>
@@ -13355,13 +13360,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H377" s="8">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c t="s" r="I377" s="7">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c t="s" r="J377" s="7">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="K377" s="7"/>
       <c r="L377" s="7"/>
@@ -13379,22 +13384,22 @@
       </c>
       <c r="D378" s="7"/>
       <c t="s" r="E378" s="7">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="F378" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G378" s="8">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c t="s" r="H378" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I378" s="7">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c t="s" r="J378" s="7">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="K378" s="7"/>
       <c r="L378" s="7"/>
@@ -13427,7 +13432,7 @@
       </c>
       <c r="D380" s="7"/>
       <c t="s" r="E380" s="7">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="F380" s="7">
         <v>321</v>
@@ -13436,13 +13441,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H380" s="8">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c t="s" r="I380" s="7">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c t="s" r="J380" s="7">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="K380" s="7"/>
       <c r="L380" s="7"/>
@@ -13460,22 +13465,22 @@
       </c>
       <c r="D381" s="7"/>
       <c t="s" r="E381" s="7">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="F381" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G381" s="8">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c t="s" r="H381" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I381" s="7">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c t="s" r="J381" s="7">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="K381" s="7"/>
       <c r="L381" s="7"/>
@@ -13486,14 +13491,14 @@
         <v>13</v>
       </c>
       <c t="s" r="B382" s="7">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c t="s" r="C382" s="7">
         <v>14</v>
       </c>
       <c r="D382" s="7"/>
       <c t="s" r="E382" s="7">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="F382" s="7">
         <v>321</v>
@@ -13502,20 +13507,20 @@
         <v>16</v>
       </c>
       <c t="s" r="H382" s="8">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c t="s" r="I382" s="7">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c t="s" r="J382" s="7">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c t="s" r="K382" s="7">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="L382" s="7"/>
       <c t="s" r="M382" s="7">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="383" ht="14.25" customHeight="1">
@@ -13523,36 +13528,36 @@
         <v>13</v>
       </c>
       <c t="s" r="B383" s="7">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c t="s" r="C383" s="7">
         <v>14</v>
       </c>
       <c r="D383" s="7"/>
       <c t="s" r="E383" s="7">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="F383" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G383" s="8">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c t="s" r="H383" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I383" s="7">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c t="s" r="J383" s="7">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c t="s" r="K383" s="7">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="L383" s="7"/>
       <c t="s" r="M383" s="7">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="384" ht="14.25" customHeight="1">
@@ -13567,7 +13572,7 @@
       </c>
       <c r="D384" s="7"/>
       <c t="s" r="E384" s="7">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="F384" s="7">
         <v>321</v>
@@ -13576,13 +13581,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H384" s="8">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c t="s" r="I384" s="7">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c t="s" r="J384" s="7">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="K384" s="7"/>
       <c r="L384" s="7"/>
@@ -13600,22 +13605,22 @@
       </c>
       <c r="D385" s="7"/>
       <c t="s" r="E385" s="7">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="F385" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G385" s="8">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c t="s" r="H385" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I385" s="7">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c t="s" r="J385" s="7">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="K385" s="7"/>
       <c r="L385" s="7"/>
@@ -13648,7 +13653,7 @@
       </c>
       <c r="D387" s="7"/>
       <c t="s" r="E387" s="7">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="F387" s="7">
         <v>320</v>
@@ -13657,13 +13662,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H387" s="8">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c t="s" r="I387" s="7">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c t="s" r="J387" s="7">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="K387" s="7"/>
       <c r="L387" s="7"/>
@@ -13681,19 +13686,19 @@
       </c>
       <c r="D388" s="7"/>
       <c t="s" r="E388" s="7">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="F388" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G388" s="8">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c t="s" r="H388" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I388" s="7">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c t="s" r="J388" s="7">
         <v>55</v>
@@ -13707,14 +13712,14 @@
         <v>13</v>
       </c>
       <c t="s" r="B389" s="7">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c t="s" r="C389" s="7">
         <v>14</v>
       </c>
       <c r="D389" s="7"/>
       <c t="s" r="E389" s="7">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="F389" s="7">
         <v>320</v>
@@ -13723,20 +13728,20 @@
         <v>16</v>
       </c>
       <c t="s" r="H389" s="8">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c t="s" r="I389" s="7">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c t="s" r="J389" s="7">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c t="s" r="K389" s="7">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="L389" s="7"/>
       <c t="s" r="M389" s="7">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="390" ht="15" customHeight="1">
@@ -13751,22 +13756,22 @@
       </c>
       <c r="D390" s="7"/>
       <c t="s" r="E390" s="7">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="F390" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G390" s="8">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c t="s" r="H390" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I390" s="7">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c t="s" r="J390" s="7">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="K390" s="7"/>
       <c r="L390" s="7"/>
@@ -13784,7 +13789,7 @@
       </c>
       <c r="D391" s="7"/>
       <c t="s" r="E391" s="7">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="F391" s="7">
         <v>320</v>
@@ -13793,13 +13798,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H391" s="8">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c t="s" r="I391" s="7">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c t="s" r="J391" s="7">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="K391" s="7"/>
       <c r="L391" s="7"/>
@@ -13817,22 +13822,22 @@
       </c>
       <c r="D392" s="7"/>
       <c t="s" r="E392" s="7">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="F392" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G392" s="8">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c t="s" r="H392" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I392" s="7">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c t="s" r="J392" s="7">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="K392" s="7"/>
       <c r="L392" s="7"/>
@@ -13850,7 +13855,7 @@
       </c>
       <c r="D393" s="7"/>
       <c t="s" r="E393" s="7">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="F393" s="7">
         <v>320</v>
@@ -13859,13 +13864,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H393" s="8">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c t="s" r="I393" s="7">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c t="s" r="J393" s="7">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="K393" s="7"/>
       <c r="L393" s="7"/>
@@ -13883,22 +13888,22 @@
       </c>
       <c r="D394" s="7"/>
       <c t="s" r="E394" s="7">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="F394" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G394" s="8">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c t="s" r="H394" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I394" s="7">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c t="s" r="J394" s="7">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="K394" s="7"/>
       <c r="L394" s="7"/>
@@ -13931,7 +13936,7 @@
       </c>
       <c r="D396" s="7"/>
       <c t="s" r="E396" s="7">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="F396" s="7">
         <v>321</v>
@@ -13940,10 +13945,10 @@
         <v>47</v>
       </c>
       <c t="s" r="H396" s="8">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c t="s" r="I396" s="7">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c t="s" r="J396" s="7">
         <v>36</v>
@@ -13964,22 +13969,22 @@
       </c>
       <c r="D397" s="7"/>
       <c t="s" r="E397" s="7">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="F397" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G397" s="8">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c t="s" r="H397" s="8">
         <v>47</v>
       </c>
       <c t="s" r="I397" s="7">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c t="s" r="J397" s="7">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="K397" s="7"/>
       <c r="L397" s="7"/>
@@ -13997,7 +14002,7 @@
       </c>
       <c r="D398" s="7"/>
       <c t="s" r="E398" s="7">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="F398" s="7">
         <v>321</v>
@@ -14006,13 +14011,13 @@
         <v>47</v>
       </c>
       <c t="s" r="H398" s="8">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c t="s" r="I398" s="7">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c t="s" r="J398" s="7">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="K398" s="7"/>
       <c r="L398" s="7"/>
@@ -14030,22 +14035,22 @@
       </c>
       <c r="D399" s="7"/>
       <c t="s" r="E399" s="7">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="F399" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G399" s="8">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c t="s" r="H399" s="8">
         <v>47</v>
       </c>
       <c t="s" r="I399" s="7">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c t="s" r="J399" s="7">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="K399" s="7"/>
       <c r="L399" s="7"/>
@@ -14056,14 +14061,14 @@
         <v>13</v>
       </c>
       <c t="s" r="B400" s="7">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c t="s" r="C400" s="7">
         <v>14</v>
       </c>
       <c r="D400" s="7"/>
       <c t="s" r="E400" s="7">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="F400" s="7">
         <v>321</v>
@@ -14072,16 +14077,16 @@
         <v>47</v>
       </c>
       <c t="s" r="H400" s="8">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c t="s" r="I400" s="7">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c t="s" r="J400" s="7">
         <v>52</v>
       </c>
       <c t="s" r="K400" s="7">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="L400" s="7"/>
       <c t="s" r="M400" s="7">
@@ -14115,29 +14120,29 @@
       </c>
       <c r="D402" s="7"/>
       <c t="s" r="E402" s="7">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="F402" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G402" s="8">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c t="s" r="H402" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I402" s="7">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c t="s" r="J402" s="7">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c t="s" r="K402" s="7">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="L402" s="7"/>
       <c t="s" r="M402" s="7">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="403" ht="14.25" customHeight="1">
@@ -14152,7 +14157,7 @@
       </c>
       <c r="D403" s="7"/>
       <c t="s" r="E403" s="7">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="F403" s="7">
         <v>330</v>
@@ -14161,13 +14166,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H403" s="8">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c t="s" r="I403" s="7">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c t="s" r="J403" s="7">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="K403" s="7"/>
       <c r="L403" s="7"/>
@@ -14200,7 +14205,7 @@
       </c>
       <c r="D405" s="7"/>
       <c t="s" r="E405" s="7">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="F405" s="7">
         <v>330</v>
@@ -14212,10 +14217,10 @@
         <v>47</v>
       </c>
       <c t="s" r="I405" s="7">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c t="s" r="J405" s="7">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="K405" s="7"/>
       <c r="L405" s="7"/>
@@ -14233,7 +14238,7 @@
       </c>
       <c r="D406" s="7"/>
       <c t="s" r="E406" s="7">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="F406" s="7">
         <v>330</v>
@@ -14242,13 +14247,13 @@
         <v>47</v>
       </c>
       <c t="s" r="H406" s="8">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c t="s" r="I406" s="7">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c t="s" r="J406" s="7">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="K406" s="7"/>
       <c r="L406" s="7"/>
@@ -14266,22 +14271,22 @@
       </c>
       <c r="D407" s="7"/>
       <c t="s" r="E407" s="7">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="F407" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G407" s="8">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c t="s" r="H407" s="8">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c t="s" r="I407" s="7">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c t="s" r="J407" s="7">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="K407" s="7"/>
       <c r="L407" s="7"/>
@@ -14299,22 +14304,22 @@
       </c>
       <c r="D408" s="7"/>
       <c t="s" r="E408" s="7">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="F408" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G408" s="8">
+        <v>433</v>
+      </c>
+      <c t="s" r="H408" s="8">
         <v>432</v>
-      </c>
-      <c t="s" r="H408" s="8">
-        <v>431</v>
       </c>
       <c t="s" r="I408" s="7">
         <v>50</v>
       </c>
       <c t="s" r="J408" s="7">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="K408" s="7"/>
       <c r="L408" s="7"/>
@@ -14347,7 +14352,7 @@
       </c>
       <c r="D410" s="7"/>
       <c t="s" r="E410" s="7">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="F410" s="7">
         <v>330</v>
@@ -14359,10 +14364,10 @@
         <v>66</v>
       </c>
       <c t="s" r="I410" s="7">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c t="s" r="J410" s="7">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="K410" s="7"/>
       <c r="L410" s="7"/>
@@ -14380,7 +14385,7 @@
       </c>
       <c r="D411" s="7"/>
       <c t="s" r="E411" s="7">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="F411" s="7">
         <v>330</v>
@@ -14389,13 +14394,13 @@
         <v>66</v>
       </c>
       <c t="s" r="H411" s="8">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c t="s" r="I411" s="7">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c t="s" r="J411" s="7">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="K411" s="7"/>
       <c r="L411" s="7"/>
@@ -14413,22 +14418,22 @@
       </c>
       <c r="D412" s="7"/>
       <c t="s" r="E412" s="7">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="F412" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G412" s="8">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c t="s" r="H412" s="8">
         <v>66</v>
       </c>
       <c t="s" r="I412" s="7">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c t="s" r="J412" s="7">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="K412" s="7"/>
       <c r="L412" s="7"/>
@@ -14461,22 +14466,22 @@
       </c>
       <c r="D414" s="7"/>
       <c t="s" r="E414" s="7">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="F414" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G414" s="8">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c t="s" r="H414" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I414" s="7">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c t="s" r="J414" s="7">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="K414" s="7"/>
       <c r="L414" s="7"/>
@@ -14494,7 +14499,7 @@
       </c>
       <c r="D415" s="7"/>
       <c t="s" r="E415" s="7">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="F415" s="7">
         <v>330</v>
@@ -14506,10 +14511,10 @@
         <v>66</v>
       </c>
       <c t="s" r="I415" s="7">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c t="s" r="J415" s="7">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="K415" s="7"/>
       <c r="L415" s="7"/>
@@ -14527,7 +14532,7 @@
       </c>
       <c r="D416" s="7"/>
       <c t="s" r="E416" s="7">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="F416" s="7">
         <v>330</v>
@@ -14536,13 +14541,13 @@
         <v>66</v>
       </c>
       <c t="s" r="H416" s="8">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c t="s" r="I416" s="7">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c t="s" r="J416" s="7">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="K416" s="7"/>
       <c r="L416" s="7"/>
@@ -14560,22 +14565,22 @@
       </c>
       <c r="D417" s="7"/>
       <c t="s" r="E417" s="7">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="F417" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G417" s="8">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c t="s" r="H417" s="8">
         <v>66</v>
       </c>
       <c t="s" r="I417" s="7">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c t="s" r="J417" s="7">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="K417" s="7"/>
       <c r="L417" s="7"/>
@@ -14608,25 +14613,25 @@
       </c>
       <c r="D419" s="7"/>
       <c t="s" r="E419" s="7">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="F419" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G419" s="8">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c t="s" r="H419" s="8">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c t="s" r="I419" s="7">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c t="s" r="J419" s="7">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c t="s" r="K419" s="7">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="L419" s="7"/>
       <c t="s" r="M419" s="7">
@@ -14645,29 +14650,29 @@
       </c>
       <c r="D420" s="7"/>
       <c t="s" r="E420" s="7">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="F420" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G420" s="8">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c t="s" r="H420" s="8">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c t="s" r="I420" s="7">
         <v>44</v>
       </c>
       <c t="s" r="J420" s="7">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c t="s" r="K420" s="7">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="L420" s="7"/>
       <c t="s" r="M420" s="7">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="421" ht="14.25" customHeight="1">
@@ -14697,7 +14702,7 @@
       </c>
       <c r="D422" s="7"/>
       <c t="s" r="E422" s="7">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="F422" s="7">
         <v>330</v>
@@ -14706,10 +14711,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H422" s="8">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c t="s" r="I422" s="7">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c t="s" r="J422" s="7">
         <v>53</v>
@@ -14730,13 +14735,13 @@
       </c>
       <c r="D423" s="7"/>
       <c t="s" r="E423" s="7">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="F423" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G423" s="8">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c t="s" r="H423" s="8">
         <v>16</v>
@@ -14745,7 +14750,7 @@
         <v>54</v>
       </c>
       <c t="s" r="J423" s="7">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="K423" s="7"/>
       <c r="L423" s="7"/>
@@ -14753,7 +14758,7 @@
     </row>
     <row r="424" ht="15.75" customHeight="1">
       <c t="s" r="A424" s="9">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B424" s="9"/>
       <c r="C424" s="9"/>
@@ -14773,7 +14778,7 @@
     <row r="425" ht="66" customHeight="1"/>
     <row r="426" ht="16.5" customHeight="1">
       <c t="s" r="A426" s="10">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="B426" s="10"/>
       <c r="C426" s="10"/>
@@ -14786,7 +14791,7 @@
       <c r="J426" s="10"/>
       <c r="K426" s="10"/>
       <c t="s" r="L426" s="11">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="M426" s="11"/>
       <c r="N426" s="11"/>
